--- a/Data Dictionary.xlsx
+++ b/Data Dictionary.xlsx
@@ -1,10 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:dbsheet="http://web.wps.cn/et/2021/dbsheet" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
-  <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="30326"/>
   <workbookPr/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Đồ_Án_PTDL_Nhóm_2.1\"/>
+    </mc:Choice>
+  </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{57B09C30-91AB-44A7-8904-017A2CC1264C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView windowWidth="13272" windowHeight="9000" activeTab="10"/>
+    <workbookView xWindow="-96" yWindow="0" windowWidth="11712" windowHeight="13056" firstSheet="6" activeTab="7" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Customers.csv" sheetId="1" r:id="rId1"/>
@@ -13,14 +19,19 @@
     <sheet name="reviews.csv" sheetId="4" r:id="rId4"/>
     <sheet name="shipments_realistic.csv" sheetId="5" r:id="rId5"/>
     <sheet name="web_traffic.csv &amp; tf.json" sheetId="6" r:id="rId6"/>
-    <sheet name="geography" sheetId="7" r:id="rId7"/>
-    <sheet name="inventory" sheetId="8" r:id="rId8"/>
+    <sheet name="inventory" sheetId="8" r:id="rId7"/>
+    <sheet name="geography" sheetId="21" r:id="rId8"/>
     <sheet name="orders_enriched" sheetId="9" r:id="rId9"/>
-    <sheet name="order_items" sheetId="10" r:id="rId10"/>
-    <sheet name="payment" sheetId="11" r:id="rId11"/>
-    <sheet name="promotions" sheetId="12" r:id="rId12"/>
-    <sheet name="products" sheetId="13" r:id="rId13"/>
-    <sheet name="returns" sheetId="14" r:id="rId14"/>
+    <sheet name="employee" sheetId="15" r:id="rId10"/>
+    <sheet name="order_items" sheetId="10" r:id="rId11"/>
+    <sheet name="customer" sheetId="16" r:id="rId12"/>
+    <sheet name="payment" sheetId="11" r:id="rId13"/>
+    <sheet name="region" sheetId="18" r:id="rId14"/>
+    <sheet name="city" sheetId="19" r:id="rId15"/>
+    <sheet name="district" sheetId="20" r:id="rId16"/>
+    <sheet name="promotions" sheetId="12" r:id="rId17"/>
+    <sheet name="products" sheetId="13" r:id="rId18"/>
+    <sheet name="returns" sheetId="14" r:id="rId19"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -31,8 +42,6 @@
         <xcalcf:feature name="microsoft.com:FV"/>
         <xcalcf:feature name="microsoft.com:CNMTM"/>
         <xcalcf:feature name="microsoft.com:LET_WF"/>
-        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
-        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
       </xcalcf:calcFeatures>
     </ext>
   </extLst>
@@ -40,7 +49,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="448" uniqueCount="251">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="508" uniqueCount="264">
   <si>
     <t>STT</t>
   </si>
@@ -438,21 +447,9 @@
     <t>Integer</t>
   </si>
   <si>
-    <t>Mã bưu chính (ZIP code), định danh duy nhất cho từng khu vực địa lý. Ví dụ: 15201, 15202...</t>
-  </si>
-  <si>
     <t>Varchar</t>
   </si>
   <si>
-    <t>Tên thành phố/tỉnh thuộc khu vực địa lý tương ứng với mã ZIP. Ví dụ: Hai Phong, Phu Ly, Viet Tri...</t>
-  </si>
-  <si>
-    <t>Vùng miền lớn mà thành phố trực thuộc, gồm 3 giá trị: East, Central, West.</t>
-  </si>
-  <si>
-    <t>Quận/huyện cụ thể trong thành phố, được đánh số dạng 'District #xx' (có 39 giá trị khác nhau).</t>
-  </si>
-  <si>
     <t>snapshot_date</t>
   </si>
   <si>
@@ -793,19 +790,124 @@
   </si>
   <si>
     <t>Số tiền hoàn trả cho lượt trả hàng, dao động từ khoảng 458.81 đến 160,937.94</t>
+  </si>
+  <si>
+    <t>Chuỗi / Ngày (Date/String)</t>
+  </si>
+  <si>
+    <t>region_id</t>
+  </si>
+  <si>
+    <t>Mã định danh duy nhất của vùng miền (ví dụ: MB, MT, MN).</t>
+  </si>
+  <si>
+    <t>region_name</t>
+  </si>
+  <si>
+    <t>Tên gọi đầy đủ của vùng miền (ví dụ: Mien Bac, Mien Trung, Mien Nam).</t>
+  </si>
+  <si>
+    <t>city_id</t>
+  </si>
+  <si>
+    <t>Mã định danh duy nhất cho từng thành phố/tỉnh (ví dụ: CT001, CT002).</t>
+  </si>
+  <si>
+    <t>city_name</t>
+  </si>
+  <si>
+    <t>Tên thành phố/tỉnh (ví dụ: Hai Phong, Phu Ly, Viet Tri).</t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">Mã vùng miền trực thuộc (dùng để liên kết với bảng </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF1F1F1F"/>
+        <rFont val="Google Sans Text"/>
+        <family val="2"/>
+      </rPr>
+      <t>REGION</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF1F1F1F"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>).</t>
+    </r>
+  </si>
+  <si>
+    <t>district_id</t>
+  </si>
+  <si>
+    <t>Mã định danh duy nhất của từng quận/huyện (ví dụ: DIS00001).</t>
+  </si>
+  <si>
+    <t>district_name</t>
+  </si>
+  <si>
+    <t>Tên quận/huyện cụ thể thuộc thành phố (ví dụ: District #13).</t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">Mã thành phố trực thuộc (dùng để liên kết với bảng </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF1F1F1F"/>
+        <rFont val="Google Sans Text"/>
+        <family val="2"/>
+      </rPr>
+      <t>CITY</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF1F1F1F"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>).</t>
+    </r>
+  </si>
+  <si>
+    <t>Mã bưu chính (ZIP code), định danh duy nhất cho từng khu vực địa lý.</t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">Mã định danh quận/huyện trực thuộc (dùng để liên kết với bảng </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF1F1F1F"/>
+        <rFont val="Google Sans Text"/>
+        <family val="2"/>
+      </rPr>
+      <t>DISTRICT</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF1F1F1F"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>).</t>
+    </r>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr9="http://schemas.microsoft.com/office/spreadsheetml/2016/revision9" mc:Ignorable="xr9">
-  <numFmts count="4">
-    <numFmt numFmtId="42" formatCode="_(&quot;$&quot;* #,##0_);_(&quot;$&quot;* \(#,##0\);_(&quot;$&quot;* &quot;-&quot;_);_(@_)"/>
-    <numFmt numFmtId="44" formatCode="_(&quot;$&quot;* #,##0.00_);_(&quot;$&quot;* \(#,##0.00\);_(&quot;$&quot;* &quot;-&quot;??_);_(@_)"/>
-    <numFmt numFmtId="176" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
-    <numFmt numFmtId="177" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;_ ;_ @_ "/>
-  </numFmts>
-  <fonts count="27">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr9="http://schemas.microsoft.com/office/spreadsheetml/2016/revision9" mc:Ignorable="x14ac x16r2 xr xr9">
+  <fonts count="14">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -857,345 +959,54 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <u/>
-      <sz val="11"/>
-      <color rgb="FF0000FF"/>
-      <name val="Calibri"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <u/>
-      <sz val="11"/>
-      <color rgb="FF800080"/>
-      <name val="Calibri"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FFFF0000"/>
-      <name val="Calibri"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="18"/>
-      <color theme="3"/>
-      <name val="Calibri"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <i/>
-      <sz val="11"/>
-      <color rgb="FF7F7F7F"/>
-      <name val="Calibri"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="15"/>
-      <color theme="3"/>
-      <name val="Calibri"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="13"/>
-      <color theme="3"/>
-      <name val="Calibri"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color theme="3"/>
-      <name val="Calibri"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF3F3F76"/>
-      <name val="Calibri"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FF3F3F3F"/>
-      <name val="Calibri"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FFFA7D00"/>
-      <name val="Calibri"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FFFFFFFF"/>
-      <name val="Calibri"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FFFA7D00"/>
-      <name val="Calibri"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
       <b/>
       <sz val="11"/>
       <color theme="1"/>
       <name val="Calibri"/>
-      <charset val="0"/>
+      <family val="2"/>
       <scheme val="minor"/>
     </font>
     <font>
-      <sz val="11"/>
-      <color rgb="FF006100"/>
-      <name val="Calibri"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF9C0006"/>
-      <name val="Calibri"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF9C6500"/>
-      <name val="Calibri"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color theme="0"/>
-      <name val="Calibri"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
+      <sz val="14"/>
+      <name val="Times New Roman"/>
+      <family val="1"/>
     </font>
     <font>
       <sz val="11"/>
       <color theme="1"/>
       <name val="Calibri"/>
-      <charset val="0"/>
+      <family val="2"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF1F1F1F"/>
+      <name val="Arial"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FF1F1F1F"/>
+      <name val="Arial"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="9"/>
+      <color rgb="FF1F1F1F"/>
+      <name val="Google Sans Text"/>
+      <family val="2"/>
+    </font>
   </fonts>
-  <fills count="33">
+  <fills count="2">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
     </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFFFCC"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFCC99"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF2F2F2"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA5A5A5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC6EFCE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFC7CE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFEB9C"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
   </fills>
-  <borders count="12">
+  <borders count="4">
     <border>
       <left/>
       <right/>
@@ -1248,295 +1059,53 @@
       </bottom>
       <diagonal/>
     </border>
-    <border>
-      <left style="thin">
-        <color rgb="FFB2B2B2"/>
-      </left>
-      <right style="thin">
-        <color rgb="FFB2B2B2"/>
-      </right>
-      <top style="thin">
-        <color rgb="FFB2B2B2"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FFB2B2B2"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="medium">
-        <color theme="4"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="medium">
-        <color theme="4" tint="0.499984740745262"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color rgb="FF7F7F7F"/>
-      </left>
-      <right style="thin">
-        <color rgb="FF7F7F7F"/>
-      </right>
-      <top style="thin">
-        <color rgb="FF7F7F7F"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FF7F7F7F"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color rgb="FF3F3F3F"/>
-      </left>
-      <right style="thin">
-        <color rgb="FF3F3F3F"/>
-      </right>
-      <top style="thin">
-        <color rgb="FF3F3F3F"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FF3F3F3F"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="double">
-        <color rgb="FF3F3F3F"/>
-      </left>
-      <right style="double">
-        <color rgb="FF3F3F3F"/>
-      </right>
-      <top style="double">
-        <color rgb="FF3F3F3F"/>
-      </top>
-      <bottom style="double">
-        <color rgb="FF3F3F3F"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="double">
-        <color rgb="FFFF8001"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top style="thin">
-        <color theme="4"/>
-      </top>
-      <bottom style="double">
-        <color theme="4"/>
-      </bottom>
-      <diagonal/>
-    </border>
   </borders>
-  <cellStyleXfs count="49">
+  <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="176" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="44" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="177" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="42" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="4" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="6" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="3" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="4" borderId="8" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="4" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="5" borderId="9" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="0" borderId="10" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="0" borderId="11" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
   </cellStyleXfs>
-  <cellXfs count="18">
+  <cellXfs count="24">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1">
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1">
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -1551,90 +1120,177 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1" indent="1" readingOrder="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1" indent="1" readingOrder="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1" indent="1" readingOrder="1"/>
+    </xf>
   </cellXfs>
-  <cellStyles count="49">
+  <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
-    <cellStyle name="Comma" xfId="1" builtinId="3"/>
-    <cellStyle name="Currency" xfId="2" builtinId="4"/>
-    <cellStyle name="Percent" xfId="3" builtinId="5"/>
-    <cellStyle name="Comma [0]" xfId="4" builtinId="6"/>
-    <cellStyle name="Currency [0]" xfId="5" builtinId="7"/>
-    <cellStyle name="Link" xfId="6" builtinId="8"/>
-    <cellStyle name="Followed Hyperlink" xfId="7" builtinId="9"/>
-    <cellStyle name="Note" xfId="8" builtinId="10"/>
-    <cellStyle name="Warning Text" xfId="9" builtinId="11"/>
-    <cellStyle name="Title" xfId="10" builtinId="15"/>
-    <cellStyle name="Explanatory Text" xfId="11" builtinId="53"/>
-    <cellStyle name="Heading 1" xfId="12" builtinId="16"/>
-    <cellStyle name="Heading 2" xfId="13" builtinId="17"/>
-    <cellStyle name="Heading 3" xfId="14" builtinId="18"/>
-    <cellStyle name="Heading 4" xfId="15" builtinId="19"/>
-    <cellStyle name="Input" xfId="16" builtinId="20"/>
-    <cellStyle name="Output" xfId="17" builtinId="21"/>
-    <cellStyle name="Calculation" xfId="18" builtinId="22"/>
-    <cellStyle name="Check Cell" xfId="19" builtinId="23"/>
-    <cellStyle name="Linked Cell" xfId="20" builtinId="24"/>
-    <cellStyle name="Total" xfId="21" builtinId="25"/>
-    <cellStyle name="Good" xfId="22" builtinId="26"/>
-    <cellStyle name="Bad" xfId="23" builtinId="27"/>
-    <cellStyle name="Neutral" xfId="24" builtinId="28"/>
-    <cellStyle name="Accent1" xfId="25" builtinId="29"/>
-    <cellStyle name="20% - Accent1" xfId="26" builtinId="30"/>
-    <cellStyle name="40% - Accent1" xfId="27" builtinId="31"/>
-    <cellStyle name="60% - Accent1" xfId="28" builtinId="32"/>
-    <cellStyle name="Accent2" xfId="29" builtinId="33"/>
-    <cellStyle name="20% - Accent2" xfId="30" builtinId="34"/>
-    <cellStyle name="40% - Accent2" xfId="31" builtinId="35"/>
-    <cellStyle name="60% - Accent2" xfId="32" builtinId="36"/>
-    <cellStyle name="Accent3" xfId="33" builtinId="37"/>
-    <cellStyle name="20% - Accent3" xfId="34" builtinId="38"/>
-    <cellStyle name="40% - Accent3" xfId="35" builtinId="39"/>
-    <cellStyle name="60% - Accent3" xfId="36" builtinId="40"/>
-    <cellStyle name="Accent4" xfId="37" builtinId="41"/>
-    <cellStyle name="20% - Accent4" xfId="38" builtinId="42"/>
-    <cellStyle name="40% - Accent4" xfId="39" builtinId="43"/>
-    <cellStyle name="60% - Accent4" xfId="40" builtinId="44"/>
-    <cellStyle name="Accent5" xfId="41" builtinId="45"/>
-    <cellStyle name="20% - Accent5" xfId="42" builtinId="46"/>
-    <cellStyle name="40% - Accent5" xfId="43" builtinId="47"/>
-    <cellStyle name="60% - Accent5" xfId="44" builtinId="48"/>
-    <cellStyle name="Accent6" xfId="45" builtinId="49"/>
-    <cellStyle name="20% - Accent6" xfId="46" builtinId="50"/>
-    <cellStyle name="40% - Accent6" xfId="47" builtinId="51"/>
-    <cellStyle name="60% - Accent6" xfId="48" builtinId="52"/>
   </cellStyles>
   <dxfs count="17">
     <dxf>
       <fill>
         <patternFill patternType="solid">
-          <fgColor theme="4" tint="0.799981688894314"/>
-          <bgColor theme="4" tint="0.799981688894314"/>
+          <fgColor theme="4" tint="0.79995117038483843"/>
+          <bgColor theme="4" tint="0.79995117038483843"/>
+        </patternFill>
+      </fill>
+      <border>
+        <bottom style="thin">
+          <color theme="4" tint="0.39994506668294322"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor theme="4" tint="0.79995117038483843"/>
+          <bgColor theme="4" tint="0.79995117038483843"/>
+        </patternFill>
+      </fill>
+      <border>
+        <bottom style="thin">
+          <color theme="4" tint="0.39994506668294322"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <color theme="1"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <color theme="1"/>
+      </font>
+      <border>
+        <bottom style="thin">
+          <color theme="4" tint="0.39994506668294322"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <color theme="1"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <color theme="1"/>
+      </font>
+      <border>
+        <top style="thin">
+          <color theme="4"/>
+        </top>
+        <bottom style="thin">
+          <color theme="4"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor theme="4" tint="0.79995117038483843"/>
+          <bgColor theme="4" tint="0.79995117038483843"/>
         </patternFill>
       </fill>
     </dxf>
     <dxf>
       <fill>
         <patternFill patternType="solid">
-          <fgColor theme="4" tint="0.799981688894314"/>
-          <bgColor theme="4" tint="0.799981688894314"/>
+          <fgColor theme="4" tint="0.79995117038483843"/>
+          <bgColor theme="4" tint="0.79995117038483843"/>
         </patternFill>
       </fill>
     </dxf>
     <dxf>
       <font>
-        <b val="1"/>
+        <b/>
+        <color theme="1"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor theme="4" tint="0.79995117038483843"/>
+          <bgColor theme="4" tint="0.79995117038483843"/>
+        </patternFill>
+      </fill>
+      <border>
+        <top style="thin">
+          <color theme="4" tint="0.39994506668294322"/>
+        </top>
+        <bottom style="thin">
+          <color theme="4" tint="0.39994506668294322"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <color theme="1"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor theme="4" tint="0.79995117038483843"/>
+          <bgColor theme="4" tint="0.79995117038483843"/>
+        </patternFill>
+      </fill>
+      <border>
+        <bottom style="thin">
+          <color theme="4" tint="0.39994506668294322"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor theme="4" tint="0.79995117038483843"/>
+          <bgColor theme="4" tint="0.79995117038483843"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor theme="4" tint="0.79995117038483843"/>
+          <bgColor theme="4" tint="0.79995117038483843"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
         <color theme="1"/>
       </font>
     </dxf>
     <dxf>
       <font>
-        <b val="1"/>
+        <b/>
         <color theme="1"/>
       </font>
     </dxf>
     <dxf>
       <font>
-        <b val="1"/>
+        <b/>
         <color theme="1"/>
       </font>
       <border>
@@ -1645,7 +1301,7 @@
     </dxf>
     <dxf>
       <font>
-        <b val="1"/>
+        <b/>
         <color theme="0"/>
       </font>
       <fill>
@@ -1673,154 +1329,40 @@
           <color theme="4"/>
         </bottom>
         <horizontal style="thin">
-          <color theme="4" tint="0.399975585192419"/>
+          <color theme="4" tint="0.39994506668294322"/>
         </horizontal>
-      </border>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor theme="4" tint="0.799981688894314"/>
-          <bgColor theme="4" tint="0.799981688894314"/>
-        </patternFill>
-      </fill>
-      <border>
-        <bottom style="thin">
-          <color theme="4" tint="0.399975585192419"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="1"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor theme="4" tint="0.799981688894314"/>
-          <bgColor theme="4" tint="0.799981688894314"/>
-        </patternFill>
-      </fill>
-      <border>
-        <bottom style="thin">
-          <color theme="4" tint="0.399975585192419"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <font>
-        <color theme="1"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <color theme="1"/>
-      </font>
-      <border>
-        <bottom style="thin">
-          <color theme="4" tint="0.399975585192419"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="1"/>
-        <color theme="1"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="1"/>
-        <color theme="1"/>
-      </font>
-      <border>
-        <top style="thin">
-          <color theme="4"/>
-        </top>
-        <bottom style="thin">
-          <color theme="4"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor theme="4" tint="0.799981688894314"/>
-          <bgColor theme="4" tint="0.799981688894314"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor theme="4" tint="0.799981688894314"/>
-          <bgColor theme="4" tint="0.799981688894314"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="1"/>
-        <color theme="1"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor theme="4" tint="0.799981688894314"/>
-          <bgColor theme="4" tint="0.799981688894314"/>
-        </patternFill>
-      </fill>
-      <border>
-        <top style="thin">
-          <color theme="4" tint="0.399975585192419"/>
-        </top>
-        <bottom style="thin">
-          <color theme="4" tint="0.399975585192419"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="1"/>
-        <color theme="1"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor theme="4" tint="0.799981688894314"/>
-          <bgColor theme="4" tint="0.799981688894314"/>
-        </patternFill>
-      </fill>
-      <border>
-        <bottom style="thin">
-          <color theme="4" tint="0.399975585192419"/>
-        </bottom>
       </border>
     </dxf>
   </dxfs>
   <tableStyles count="2" defaultTableStyle="TableStylePreset3_Accent1" defaultPivotStyle="PivotStylePreset2_Accent1">
     <tableStyle name="TableStylePreset3_Accent1" pivot="0" count="7" xr9:uid="{59DB682C-5494-4EDE-A608-00C9E5F0F923}">
-      <tableStyleElement type="wholeTable" dxfId="6"/>
-      <tableStyleElement type="headerRow" dxfId="5"/>
-      <tableStyleElement type="totalRow" dxfId="4"/>
-      <tableStyleElement type="firstColumn" dxfId="3"/>
-      <tableStyleElement type="lastColumn" dxfId="2"/>
-      <tableStyleElement type="firstRowStripe" dxfId="1"/>
-      <tableStyleElement type="firstColumnStripe" dxfId="0"/>
+      <tableStyleElement type="wholeTable" dxfId="16"/>
+      <tableStyleElement type="headerRow" dxfId="15"/>
+      <tableStyleElement type="totalRow" dxfId="14"/>
+      <tableStyleElement type="firstColumn" dxfId="13"/>
+      <tableStyleElement type="lastColumn" dxfId="12"/>
+      <tableStyleElement type="firstRowStripe" dxfId="11"/>
+      <tableStyleElement type="firstColumnStripe" dxfId="10"/>
     </tableStyle>
     <tableStyle name="PivotStylePreset2_Accent1" table="0" count="10" xr9:uid="{267968C8-6FFD-4C36-ACC1-9EA1FD1885CA}">
-      <tableStyleElement type="headerRow" dxfId="16"/>
-      <tableStyleElement type="totalRow" dxfId="15"/>
-      <tableStyleElement type="firstRowStripe" dxfId="14"/>
-      <tableStyleElement type="firstColumnStripe" dxfId="13"/>
-      <tableStyleElement type="firstSubtotalRow" dxfId="12"/>
-      <tableStyleElement type="secondSubtotalRow" dxfId="11"/>
-      <tableStyleElement type="firstRowSubheading" dxfId="10"/>
-      <tableStyleElement type="secondRowSubheading" dxfId="9"/>
-      <tableStyleElement type="pageFieldLabels" dxfId="8"/>
-      <tableStyleElement type="pageFieldValues" dxfId="7"/>
+      <tableStyleElement type="headerRow" dxfId="9"/>
+      <tableStyleElement type="totalRow" dxfId="8"/>
+      <tableStyleElement type="firstRowStripe" dxfId="7"/>
+      <tableStyleElement type="firstColumnStripe" dxfId="6"/>
+      <tableStyleElement type="firstSubtotalRow" dxfId="5"/>
+      <tableStyleElement type="secondSubtotalRow" dxfId="4"/>
+      <tableStyleElement type="firstRowSubheading" dxfId="3"/>
+      <tableStyleElement type="secondRowSubheading" dxfId="2"/>
+      <tableStyleElement type="pageFieldLabels" dxfId="1"/>
+      <tableStyleElement type="pageFieldValues" dxfId="0"/>
     </tableStyle>
   </tableStyles>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
       <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
+    </ext>
+    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
+      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
     </ext>
   </extLst>
 </styleSheet>
@@ -2070,23 +1612,23 @@
     </a:fmtScheme>
   </a:themeElements>
   <a:objectDefaults/>
+  <a:extraClrSchemeLst/>
 </a:theme>
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
-  <sheetPr/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:D8"/>
-  <sheetFormatPr defaultColWidth="8.88888888888889" defaultRowHeight="18" outlineLevelRow="7" outlineLevelCol="3"/>
+  <sheetFormatPr defaultColWidth="8.88671875" defaultRowHeight="18"/>
   <cols>
-    <col min="1" max="1" width="6.77777777777778" style="16" customWidth="1"/>
-    <col min="2" max="2" width="27.8888888888889" style="1" customWidth="1"/>
-    <col min="3" max="3" width="29.6666666666667" style="1" customWidth="1"/>
-    <col min="4" max="4" width="66.4444444444444" style="1" customWidth="1"/>
-    <col min="5" max="16384" width="8.88888888888889" style="1"/>
+    <col min="1" max="1" width="6.77734375" style="16" customWidth="1"/>
+    <col min="2" max="2" width="27.88671875" style="1" customWidth="1"/>
+    <col min="3" max="3" width="29.6640625" style="1" customWidth="1"/>
+    <col min="4" max="4" width="66.44140625" style="1" customWidth="1"/>
+    <col min="5" max="16384" width="8.88671875" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" s="10" customFormat="1" ht="17.4" spans="1:4">
+    <row r="1" spans="1:4" s="10" customFormat="1" ht="17.399999999999999">
       <c r="A1" s="14" t="s">
         <v>0</v>
       </c>
@@ -2200,126 +1742,273 @@
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-  <headerFooter/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
-  <sheetPr/>
-  <dimension ref="A1:C8"/>
-  <sheetFormatPr defaultColWidth="8.88888888888889" defaultRowHeight="18" outlineLevelRow="7" outlineLevelCol="2"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{61EFBDAE-EAB8-41C5-BB88-AE4529FFB780}">
+  <dimension ref="A1:C4"/>
+  <sheetFormatPr defaultRowHeight="14.4"/>
   <cols>
-    <col min="1" max="1" width="38.5555555555556" style="1" customWidth="1"/>
-    <col min="2" max="2" width="27.8888888888889" style="1" customWidth="1"/>
-    <col min="3" max="3" width="50.2222222222222" style="1" customWidth="1"/>
-    <col min="4" max="16384" width="8.88888888888889" style="1"/>
+    <col min="1" max="1" width="16.5546875" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="11" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="64.44140625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" s="6" customFormat="1" spans="1:3">
-      <c r="A1" s="7" t="s">
+    <row r="1" spans="1:3">
+      <c r="A1" s="18" t="s">
         <v>130</v>
       </c>
-      <c r="B1" s="7" t="s">
+      <c r="B1" s="18" t="s">
         <v>2</v>
       </c>
-      <c r="C1" s="7" t="s">
+      <c r="C1" s="18" t="s">
         <v>3</v>
       </c>
     </row>
-    <row r="2" ht="54" spans="1:3">
-      <c r="A2" s="8" t="s">
-        <v>61</v>
-      </c>
-      <c r="B2" s="8" t="s">
+    <row r="2" spans="1:3">
+      <c r="A2" t="s">
+        <v>182</v>
+      </c>
+      <c r="B2" s="20" t="s">
+        <v>132</v>
+      </c>
+      <c r="C2" t="s">
+        <v>183</v>
+      </c>
+    </row>
+    <row r="3" spans="1:3">
+      <c r="A3" t="s">
+        <v>184</v>
+      </c>
+      <c r="B3" s="20" t="s">
+        <v>132</v>
+      </c>
+      <c r="C3" t="s">
+        <v>185</v>
+      </c>
+    </row>
+    <row r="4" spans="1:3">
+      <c r="A4" t="s">
+        <v>190</v>
+      </c>
+      <c r="B4" s="20" t="s">
         <v>131</v>
       </c>
-      <c r="C2" s="8" t="s">
-        <v>199</v>
-      </c>
-    </row>
-    <row r="3" ht="54" spans="1:3">
-      <c r="A3" s="8" t="s">
-        <v>21</v>
-      </c>
-      <c r="B3" s="8" t="s">
-        <v>131</v>
-      </c>
-      <c r="C3" s="8" t="s">
-        <v>200</v>
-      </c>
-    </row>
-    <row r="4" ht="36" spans="1:3">
-      <c r="A4" s="8" t="s">
-        <v>201</v>
-      </c>
-      <c r="B4" s="8" t="s">
-        <v>131</v>
-      </c>
-      <c r="C4" s="8" t="s">
-        <v>202</v>
-      </c>
-    </row>
-    <row r="5" ht="36" spans="1:3">
-      <c r="A5" s="8" t="s">
-        <v>203</v>
-      </c>
-      <c r="B5" s="8" t="s">
-        <v>150</v>
-      </c>
-      <c r="C5" s="8" t="s">
-        <v>204</v>
-      </c>
-    </row>
-    <row r="6" ht="54" spans="1:3">
-      <c r="A6" s="8" t="s">
-        <v>205</v>
-      </c>
-      <c r="B6" s="8" t="s">
-        <v>150</v>
-      </c>
-      <c r="C6" s="8" t="s">
-        <v>206</v>
-      </c>
-    </row>
-    <row r="7" ht="72" spans="1:3">
-      <c r="A7" s="8" t="s">
-        <v>38</v>
-      </c>
-      <c r="B7" s="8" t="s">
-        <v>197</v>
-      </c>
-      <c r="C7" s="8" t="s">
-        <v>207</v>
-      </c>
-    </row>
-    <row r="8" ht="54" spans="1:3">
-      <c r="A8" s="8" t="s">
-        <v>208</v>
-      </c>
-      <c r="B8" s="8" t="s">
-        <v>197</v>
-      </c>
-      <c r="C8" s="8" t="s">
-        <v>209</v>
+      <c r="C4" t="s">
+        <v>191</v>
       </c>
     </row>
   </sheetData>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-  <headerFooter/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
-  <sheetPr/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0900-000000000000}">
   <dimension ref="A1:C8"/>
-  <sheetFormatPr defaultColWidth="8.88888888888889" defaultRowHeight="18" outlineLevelRow="7" outlineLevelCol="2"/>
+  <sheetFormatPr defaultColWidth="8.88671875" defaultRowHeight="18"/>
   <cols>
-    <col min="1" max="1" width="27.2222222222222" style="1" customWidth="1"/>
-    <col min="2" max="2" width="33.7777777777778" style="1" customWidth="1"/>
-    <col min="3" max="3" width="44.3333333333333" style="1" customWidth="1"/>
-    <col min="4" max="16384" width="8.88888888888889" style="1"/>
+    <col min="1" max="1" width="38.5546875" style="1" customWidth="1"/>
+    <col min="2" max="2" width="27.88671875" style="1" customWidth="1"/>
+    <col min="3" max="3" width="50.21875" style="1" customWidth="1"/>
+    <col min="4" max="16384" width="8.88671875" style="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:3" s="6" customFormat="1">
+      <c r="A1" s="7" t="s">
+        <v>130</v>
+      </c>
+      <c r="B1" s="7" t="s">
+        <v>2</v>
+      </c>
+      <c r="C1" s="7" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="2" spans="1:3" ht="54">
+      <c r="A2" s="8" t="s">
+        <v>61</v>
+      </c>
+      <c r="B2" s="8" t="s">
+        <v>131</v>
+      </c>
+      <c r="C2" s="8" t="s">
+        <v>195</v>
+      </c>
+    </row>
+    <row r="3" spans="1:3" ht="54">
+      <c r="A3" s="8" t="s">
+        <v>21</v>
+      </c>
+      <c r="B3" s="8" t="s">
+        <v>131</v>
+      </c>
+      <c r="C3" s="8" t="s">
+        <v>196</v>
+      </c>
+    </row>
+    <row r="4" spans="1:3" ht="36">
+      <c r="A4" s="8" t="s">
+        <v>197</v>
+      </c>
+      <c r="B4" s="8" t="s">
+        <v>131</v>
+      </c>
+      <c r="C4" s="8" t="s">
+        <v>198</v>
+      </c>
+    </row>
+    <row r="5" spans="1:3" ht="36">
+      <c r="A5" s="8" t="s">
+        <v>199</v>
+      </c>
+      <c r="B5" s="8" t="s">
+        <v>146</v>
+      </c>
+      <c r="C5" s="8" t="s">
+        <v>200</v>
+      </c>
+    </row>
+    <row r="6" spans="1:3" ht="54">
+      <c r="A6" s="8" t="s">
+        <v>201</v>
+      </c>
+      <c r="B6" s="8" t="s">
+        <v>146</v>
+      </c>
+      <c r="C6" s="8" t="s">
+        <v>202</v>
+      </c>
+    </row>
+    <row r="7" spans="1:3" ht="72">
+      <c r="A7" s="8" t="s">
+        <v>38</v>
+      </c>
+      <c r="B7" s="8" t="s">
+        <v>193</v>
+      </c>
+      <c r="C7" s="8" t="s">
+        <v>203</v>
+      </c>
+    </row>
+    <row r="8" spans="1:3" ht="72">
+      <c r="A8" s="8" t="s">
+        <v>204</v>
+      </c>
+      <c r="B8" s="8" t="s">
+        <v>193</v>
+      </c>
+      <c r="C8" s="8" t="s">
+        <v>205</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D95C202C-0552-40EC-83B4-6358B4060693}">
+  <dimension ref="A1:C7"/>
+  <sheetFormatPr defaultRowHeight="14.4"/>
+  <cols>
+    <col min="1" max="1" width="17.44140625" customWidth="1"/>
+    <col min="2" max="2" width="22.109375" customWidth="1"/>
+    <col min="3" max="3" width="24.44140625" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:3" ht="42" thickBot="1">
+      <c r="A1" s="21" t="s">
+        <v>130</v>
+      </c>
+      <c r="B1" s="21" t="s">
+        <v>2</v>
+      </c>
+      <c r="C1" s="21" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="2" spans="1:3" ht="124.8" thickBot="1">
+      <c r="A2" s="22" t="s">
+        <v>4</v>
+      </c>
+      <c r="B2" s="23" t="s">
+        <v>5</v>
+      </c>
+      <c r="C2" s="23" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="3" spans="1:3" ht="111" thickBot="1">
+      <c r="A3" s="22" t="s">
+        <v>12</v>
+      </c>
+      <c r="B3" s="23" t="s">
+        <v>247</v>
+      </c>
+      <c r="C3" s="23" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="4" spans="1:3" ht="69.599999999999994" thickBot="1">
+      <c r="A4" s="22" t="s">
+        <v>15</v>
+      </c>
+      <c r="B4" s="23" t="s">
+        <v>10</v>
+      </c>
+      <c r="C4" s="23" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="5" spans="1:3" ht="69.599999999999994" thickBot="1">
+      <c r="A5" s="22" t="s">
+        <v>17</v>
+      </c>
+      <c r="B5" s="23" t="s">
+        <v>10</v>
+      </c>
+      <c r="C5" s="23" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="6" spans="1:3" ht="111" thickBot="1">
+      <c r="A6" s="22" t="s">
+        <v>19</v>
+      </c>
+      <c r="B6" s="23" t="s">
+        <v>10</v>
+      </c>
+      <c r="C6" s="23" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="7" spans="1:3" ht="166.2" thickBot="1">
+      <c r="A7" s="22" t="s">
+        <v>7</v>
+      </c>
+      <c r="B7" s="23" t="s">
+        <v>5</v>
+      </c>
+      <c r="C7" s="23" t="s">
+        <v>8</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0A00-000000000000}">
+  <dimension ref="A1:C8"/>
+  <sheetFormatPr defaultColWidth="8.88671875" defaultRowHeight="18"/>
+  <cols>
+    <col min="1" max="1" width="27.21875" style="1" customWidth="1"/>
+    <col min="2" max="2" width="33.77734375" style="1" customWidth="1"/>
+    <col min="3" max="3" width="44.33203125" style="1" customWidth="1"/>
+    <col min="4" max="16384" width="8.88671875" style="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:3">
@@ -2333,48 +2022,48 @@
         <v>3</v>
       </c>
     </row>
-    <row r="2" ht="54" spans="1:3">
+    <row r="2" spans="1:3" ht="54">
       <c r="A2" s="5" t="s">
         <v>61</v>
       </c>
       <c r="B2" s="5" t="s">
+        <v>206</v>
+      </c>
+      <c r="C2" s="5" t="s">
+        <v>207</v>
+      </c>
+    </row>
+    <row r="3" spans="1:3" ht="90">
+      <c r="A3" s="5" t="s">
+        <v>176</v>
+      </c>
+      <c r="B3" s="5" t="s">
+        <v>208</v>
+      </c>
+      <c r="C3" s="5" t="s">
+        <v>209</v>
+      </c>
+    </row>
+    <row r="4" spans="1:3" ht="54">
+      <c r="A4" s="5" t="s">
         <v>210</v>
       </c>
-      <c r="C2" s="5" t="s">
+      <c r="B4" s="5" t="s">
         <v>211</v>
       </c>
-    </row>
-    <row r="3" ht="90" spans="1:3">
-      <c r="A3" s="5" t="s">
-        <v>180</v>
-      </c>
-      <c r="B3" s="5" t="s">
+      <c r="C4" s="5" t="s">
         <v>212</v>
       </c>
-      <c r="C3" s="5" t="s">
+    </row>
+    <row r="5" spans="1:3" ht="36">
+      <c r="A5" s="5" t="s">
         <v>213</v>
       </c>
-    </row>
-    <row r="4" ht="54" spans="1:3">
-      <c r="A4" s="5" t="s">
+      <c r="B5" s="5" t="s">
+        <v>206</v>
+      </c>
+      <c r="C5" s="5" t="s">
         <v>214</v>
-      </c>
-      <c r="B4" s="5" t="s">
-        <v>215</v>
-      </c>
-      <c r="C4" s="5" t="s">
-        <v>216</v>
-      </c>
-    </row>
-    <row r="5" ht="36" spans="1:3">
-      <c r="A5" s="5" t="s">
-        <v>217</v>
-      </c>
-      <c r="B5" s="5" t="s">
-        <v>210</v>
-      </c>
-      <c r="C5" s="5" t="s">
-        <v>218</v>
       </c>
     </row>
     <row r="6" spans="1:3">
@@ -2394,20 +2083,183 @@
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-  <headerFooter/>
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
-  <sheetPr/>
+<file path=xl/worksheets/sheet14.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1456BB1E-F52F-40CF-B18F-4C959AB21721}">
+  <dimension ref="A1:C3"/>
+  <sheetFormatPr defaultRowHeight="14.4"/>
+  <cols>
+    <col min="1" max="2" width="14.88671875" customWidth="1"/>
+    <col min="3" max="3" width="36.109375" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:3" ht="42" thickBot="1">
+      <c r="A1" s="21" t="s">
+        <v>130</v>
+      </c>
+      <c r="B1" s="21" t="s">
+        <v>2</v>
+      </c>
+      <c r="C1" s="21" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="2" spans="1:3" ht="166.2" thickBot="1">
+      <c r="A2" s="22" t="s">
+        <v>248</v>
+      </c>
+      <c r="B2" s="23" t="s">
+        <v>10</v>
+      </c>
+      <c r="C2" s="23" t="s">
+        <v>249</v>
+      </c>
+    </row>
+    <row r="3" spans="1:3" ht="166.2" thickBot="1">
+      <c r="A3" s="22" t="s">
+        <v>250</v>
+      </c>
+      <c r="B3" s="23" t="s">
+        <v>10</v>
+      </c>
+      <c r="C3" s="23" t="s">
+        <v>251</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet15.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{AEC1F8BA-98B3-46C3-8F38-171796BF0C73}">
+  <dimension ref="A1:C4"/>
+  <sheetFormatPr defaultRowHeight="14.4"/>
+  <cols>
+    <col min="1" max="1" width="25.109375" customWidth="1"/>
+    <col min="2" max="2" width="31.44140625" customWidth="1"/>
+    <col min="3" max="3" width="35" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:3" ht="42" thickBot="1">
+      <c r="A1" s="21" t="s">
+        <v>130</v>
+      </c>
+      <c r="B1" s="21" t="s">
+        <v>2</v>
+      </c>
+      <c r="C1" s="21" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="2" spans="1:3" ht="207.6" thickBot="1">
+      <c r="A2" s="22" t="s">
+        <v>252</v>
+      </c>
+      <c r="B2" s="23" t="s">
+        <v>10</v>
+      </c>
+      <c r="C2" s="23" t="s">
+        <v>253</v>
+      </c>
+    </row>
+    <row r="3" spans="1:3" ht="124.8" thickBot="1">
+      <c r="A3" s="22" t="s">
+        <v>254</v>
+      </c>
+      <c r="B3" s="23" t="s">
+        <v>10</v>
+      </c>
+      <c r="C3" s="23" t="s">
+        <v>255</v>
+      </c>
+    </row>
+    <row r="4" spans="1:3" ht="150" thickBot="1">
+      <c r="A4" s="22" t="s">
+        <v>248</v>
+      </c>
+      <c r="B4" s="23" t="s">
+        <v>10</v>
+      </c>
+      <c r="C4" s="23" t="s">
+        <v>256</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet16.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{0DC09820-A76E-48BA-B097-1044F967E90C}">
+  <dimension ref="A1:C4"/>
+  <sheetFormatPr defaultRowHeight="14.4"/>
+  <cols>
+    <col min="1" max="1" width="17.44140625" customWidth="1"/>
+    <col min="2" max="2" width="21.88671875" customWidth="1"/>
+    <col min="3" max="3" width="26.109375" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:3" ht="42" thickBot="1">
+      <c r="A1" s="21" t="s">
+        <v>130</v>
+      </c>
+      <c r="B1" s="21" t="s">
+        <v>2</v>
+      </c>
+      <c r="C1" s="21" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="2" spans="1:3" ht="166.2" thickBot="1">
+      <c r="A2" s="22" t="s">
+        <v>257</v>
+      </c>
+      <c r="B2" s="23" t="s">
+        <v>10</v>
+      </c>
+      <c r="C2" s="23" t="s">
+        <v>258</v>
+      </c>
+    </row>
+    <row r="3" spans="1:3" ht="138.6" thickBot="1">
+      <c r="A3" s="22" t="s">
+        <v>259</v>
+      </c>
+      <c r="B3" s="23" t="s">
+        <v>10</v>
+      </c>
+      <c r="C3" s="23" t="s">
+        <v>260</v>
+      </c>
+    </row>
+    <row r="4" spans="1:3" ht="138.6" thickBot="1">
+      <c r="A4" s="22" t="s">
+        <v>252</v>
+      </c>
+      <c r="B4" s="23" t="s">
+        <v>10</v>
+      </c>
+      <c r="C4" s="23" t="s">
+        <v>261</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet17.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0B00-000000000000}">
   <dimension ref="A1:C11"/>
-  <sheetFormatPr defaultColWidth="8.88888888888889" defaultRowHeight="18" outlineLevelCol="2"/>
+  <sheetFormatPr defaultColWidth="8.88671875" defaultRowHeight="18"/>
   <cols>
-    <col min="1" max="1" width="31.4444444444444" style="1" customWidth="1"/>
-    <col min="2" max="2" width="30.8888888888889" style="1" customWidth="1"/>
-    <col min="3" max="3" width="49.3333333333333" style="1" customWidth="1"/>
-    <col min="4" max="16384" width="8.88888888888889" style="1"/>
+    <col min="1" max="1" width="31.44140625" style="1" customWidth="1"/>
+    <col min="2" max="2" width="30.88671875" style="1" customWidth="1"/>
+    <col min="3" max="3" width="49.33203125" style="1" customWidth="1"/>
+    <col min="4" max="16384" width="8.88671875" style="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:3">
@@ -2421,132 +2273,130 @@
         <v>3</v>
       </c>
     </row>
-    <row r="2" ht="36" spans="1:3">
+    <row r="2" spans="1:3" ht="36">
       <c r="A2" s="3" t="s">
         <v>38</v>
       </c>
       <c r="B2" s="3" t="s">
-        <v>212</v>
+        <v>208</v>
       </c>
       <c r="C2" s="3" t="s">
-        <v>219</v>
-      </c>
-    </row>
-    <row r="3" ht="36" spans="1:3">
+        <v>215</v>
+      </c>
+    </row>
+    <row r="3" spans="1:3" ht="36">
       <c r="A3" s="3" t="s">
         <v>40</v>
       </c>
       <c r="B3" s="3" t="s">
-        <v>212</v>
+        <v>208</v>
       </c>
       <c r="C3" s="3" t="s">
-        <v>220</v>
-      </c>
-    </row>
-    <row r="4" ht="54" spans="1:3">
+        <v>216</v>
+      </c>
+    </row>
+    <row r="4" spans="1:3" ht="54">
       <c r="A4" s="3" t="s">
         <v>42</v>
       </c>
       <c r="B4" s="3" t="s">
-        <v>212</v>
+        <v>208</v>
       </c>
       <c r="C4" s="3" t="s">
-        <v>221</v>
-      </c>
-    </row>
-    <row r="5" ht="36" spans="1:3">
+        <v>217</v>
+      </c>
+    </row>
+    <row r="5" spans="1:3" ht="36">
       <c r="A5" s="3" t="s">
         <v>44</v>
       </c>
       <c r="B5" s="3" t="s">
-        <v>215</v>
+        <v>211</v>
       </c>
       <c r="C5" s="3" t="s">
-        <v>222</v>
-      </c>
-    </row>
-    <row r="6" ht="36" spans="1:3">
+        <v>218</v>
+      </c>
+    </row>
+    <row r="6" spans="1:3" ht="36">
       <c r="A6" s="3" t="s">
         <v>46</v>
       </c>
       <c r="B6" s="3" t="s">
-        <v>223</v>
+        <v>219</v>
       </c>
       <c r="C6" s="3" t="s">
-        <v>224</v>
-      </c>
-    </row>
-    <row r="7" ht="36" spans="1:3">
+        <v>220</v>
+      </c>
+    </row>
+    <row r="7" spans="1:3" ht="36">
       <c r="A7" s="3" t="s">
         <v>48</v>
       </c>
       <c r="B7" s="3" t="s">
-        <v>223</v>
+        <v>219</v>
       </c>
       <c r="C7" s="3" t="s">
-        <v>225</v>
-      </c>
-    </row>
-    <row r="8" ht="54" spans="1:3">
+        <v>221</v>
+      </c>
+    </row>
+    <row r="8" spans="1:3" ht="54">
       <c r="A8" s="3" t="s">
         <v>50</v>
       </c>
       <c r="B8" s="3" t="s">
-        <v>212</v>
+        <v>208</v>
       </c>
       <c r="C8" s="3" t="s">
-        <v>226</v>
-      </c>
-    </row>
-    <row r="9" ht="54" spans="1:3">
+        <v>222</v>
+      </c>
+    </row>
+    <row r="9" spans="1:3" ht="54">
       <c r="A9" s="3" t="s">
         <v>52</v>
       </c>
       <c r="B9" s="3" t="s">
-        <v>212</v>
+        <v>208</v>
       </c>
       <c r="C9" s="3" t="s">
-        <v>227</v>
-      </c>
-    </row>
-    <row r="10" ht="54" spans="1:3">
+        <v>223</v>
+      </c>
+    </row>
+    <row r="10" spans="1:3" ht="54">
       <c r="A10" s="3" t="s">
         <v>54</v>
       </c>
       <c r="B10" s="3" t="s">
-        <v>228</v>
+        <v>224</v>
       </c>
       <c r="C10" s="3" t="s">
-        <v>229</v>
-      </c>
-    </row>
-    <row r="11" ht="54" spans="1:3">
+        <v>225</v>
+      </c>
+    </row>
+    <row r="11" spans="1:3" ht="54">
       <c r="A11" s="3" t="s">
         <v>56</v>
       </c>
       <c r="B11" s="3" t="s">
-        <v>210</v>
+        <v>206</v>
       </c>
       <c r="C11" s="3" t="s">
-        <v>230</v>
+        <v>226</v>
       </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-  <headerFooter/>
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
-  <sheetPr/>
+<file path=xl/worksheets/sheet18.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0C00-000000000000}">
   <dimension ref="A1:C9"/>
-  <sheetFormatPr defaultColWidth="8.88888888888889" defaultRowHeight="18" outlineLevelCol="2"/>
+  <sheetFormatPr defaultColWidth="8.88671875" defaultRowHeight="18"/>
   <cols>
-    <col min="1" max="1" width="20.7777777777778" style="1" customWidth="1"/>
-    <col min="2" max="2" width="24.8888888888889" style="1" customWidth="1"/>
-    <col min="3" max="3" width="63.2222222222222" style="1" customWidth="1"/>
-    <col min="4" max="16384" width="8.88888888888889" style="1"/>
+    <col min="1" max="1" width="20.77734375" style="1" customWidth="1"/>
+    <col min="2" max="2" width="24.88671875" style="1" customWidth="1"/>
+    <col min="3" max="3" width="63.21875" style="1" customWidth="1"/>
+    <col min="4" max="16384" width="8.88671875" style="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:3">
@@ -2565,43 +2415,43 @@
         <v>21</v>
       </c>
       <c r="B2" s="3" t="s">
-        <v>210</v>
+        <v>206</v>
       </c>
       <c r="C2" s="3" t="s">
-        <v>231</v>
-      </c>
-    </row>
-    <row r="3" ht="36" spans="1:3">
+        <v>227</v>
+      </c>
+    </row>
+    <row r="3" spans="1:3" ht="36">
       <c r="A3" s="3" t="s">
         <v>23</v>
       </c>
       <c r="B3" s="3" t="s">
-        <v>212</v>
+        <v>208</v>
       </c>
       <c r="C3" s="3" t="s">
-        <v>232</v>
-      </c>
-    </row>
-    <row r="4" ht="36" spans="1:3">
+        <v>228</v>
+      </c>
+    </row>
+    <row r="4" spans="1:3" ht="36">
       <c r="A4" s="3" t="s">
         <v>25</v>
       </c>
       <c r="B4" s="3" t="s">
-        <v>212</v>
+        <v>208</v>
       </c>
       <c r="C4" s="3" t="s">
-        <v>233</v>
-      </c>
-    </row>
-    <row r="5" ht="54" spans="1:3">
+        <v>229</v>
+      </c>
+    </row>
+    <row r="5" spans="1:3" ht="54">
       <c r="A5" s="3" t="s">
         <v>27</v>
       </c>
       <c r="B5" s="3" t="s">
-        <v>212</v>
+        <v>208</v>
       </c>
       <c r="C5" s="3" t="s">
-        <v>234</v>
+        <v>230</v>
       </c>
     </row>
     <row r="6" spans="1:3">
@@ -2609,61 +2459,59 @@
         <v>29</v>
       </c>
       <c r="B6" s="3" t="s">
-        <v>212</v>
+        <v>208</v>
       </c>
       <c r="C6" s="3" t="s">
-        <v>235</v>
-      </c>
-    </row>
-    <row r="7" ht="36" spans="1:3">
+        <v>231</v>
+      </c>
+    </row>
+    <row r="7" spans="1:3" ht="36">
       <c r="A7" s="3" t="s">
         <v>31</v>
       </c>
       <c r="B7" s="3" t="s">
-        <v>212</v>
+        <v>208</v>
       </c>
       <c r="C7" s="3" t="s">
-        <v>236</v>
-      </c>
-    </row>
-    <row r="8" spans="1:3">
+        <v>232</v>
+      </c>
+    </row>
+    <row r="8" spans="1:3" ht="36">
       <c r="A8" s="3" t="s">
         <v>33</v>
       </c>
       <c r="B8" s="3" t="s">
-        <v>215</v>
+        <v>211</v>
       </c>
       <c r="C8" s="3" t="s">
-        <v>237</v>
-      </c>
-    </row>
-    <row r="9" ht="36" spans="1:3">
+        <v>233</v>
+      </c>
+    </row>
+    <row r="9" spans="1:3" ht="36">
       <c r="A9" s="3" t="s">
         <v>36</v>
       </c>
       <c r="B9" s="3" t="s">
-        <v>215</v>
+        <v>211</v>
       </c>
       <c r="C9" s="3" t="s">
-        <v>238</v>
+        <v>234</v>
       </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-  <headerFooter/>
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet14.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
-  <sheetPr/>
+<file path=xl/worksheets/sheet19.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0D00-000000000000}">
   <dimension ref="A1:C8"/>
-  <sheetFormatPr defaultColWidth="8.88888888888889" defaultRowHeight="18" outlineLevelRow="7" outlineLevelCol="2"/>
+  <sheetFormatPr defaultColWidth="8.88671875" defaultRowHeight="18"/>
   <cols>
-    <col min="1" max="1" width="33.2222222222222" style="1" customWidth="1"/>
-    <col min="2" max="2" width="30.3333333333333" style="1" customWidth="1"/>
-    <col min="3" max="3" width="39.5555555555556" style="1" customWidth="1"/>
-    <col min="4" max="16384" width="8.88888888888889" style="1"/>
+    <col min="1" max="1" width="33.21875" style="1" customWidth="1"/>
+    <col min="2" max="2" width="30.33203125" style="1" customWidth="1"/>
+    <col min="3" max="3" width="39.5546875" style="1" customWidth="1"/>
+    <col min="4" max="16384" width="8.88671875" style="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:3">
@@ -2677,102 +2525,100 @@
         <v>3</v>
       </c>
     </row>
-    <row r="2" ht="36" spans="1:3">
+    <row r="2" spans="1:3" ht="36">
       <c r="A2" s="3" t="s">
-        <v>239</v>
+        <v>235</v>
       </c>
       <c r="B2" s="3" t="s">
-        <v>212</v>
+        <v>208</v>
       </c>
       <c r="C2" s="3" t="s">
-        <v>240</v>
-      </c>
-    </row>
-    <row r="3" ht="54" spans="1:3">
+        <v>236</v>
+      </c>
+    </row>
+    <row r="3" spans="1:3" ht="54">
       <c r="A3" s="3" t="s">
         <v>61</v>
       </c>
       <c r="B3" s="3" t="s">
-        <v>210</v>
+        <v>206</v>
       </c>
       <c r="C3" s="3" t="s">
-        <v>241</v>
-      </c>
-    </row>
-    <row r="4" ht="36" spans="1:3">
+        <v>237</v>
+      </c>
+    </row>
+    <row r="4" spans="1:3" ht="36">
       <c r="A4" s="3" t="s">
         <v>21</v>
       </c>
       <c r="B4" s="3" t="s">
-        <v>210</v>
+        <v>206</v>
       </c>
       <c r="C4" s="3" t="s">
+        <v>238</v>
+      </c>
+    </row>
+    <row r="5" spans="1:3" ht="54">
+      <c r="A5" s="3" t="s">
+        <v>239</v>
+      </c>
+      <c r="B5" s="3" t="s">
+        <v>219</v>
+      </c>
+      <c r="C5" s="3" t="s">
+        <v>240</v>
+      </c>
+    </row>
+    <row r="6" spans="1:3" ht="108">
+      <c r="A6" s="3" t="s">
+        <v>241</v>
+      </c>
+      <c r="B6" s="3" t="s">
+        <v>208</v>
+      </c>
+      <c r="C6" s="3" t="s">
         <v>242</v>
       </c>
     </row>
-    <row r="5" ht="54" spans="1:3">
-      <c r="A5" s="3" t="s">
+    <row r="7" spans="1:3" ht="36">
+      <c r="A7" s="3" t="s">
         <v>243</v>
       </c>
-      <c r="B5" s="3" t="s">
-        <v>223</v>
-      </c>
-      <c r="C5" s="3" t="s">
+      <c r="B7" s="3" t="s">
+        <v>206</v>
+      </c>
+      <c r="C7" s="3" t="s">
         <v>244</v>
       </c>
     </row>
-    <row r="6" ht="108" spans="1:3">
-      <c r="A6" s="3" t="s">
+    <row r="8" spans="1:3" ht="54">
+      <c r="A8" s="3" t="s">
         <v>245</v>
       </c>
-      <c r="B6" s="3" t="s">
-        <v>212</v>
-      </c>
-      <c r="C6" s="3" t="s">
+      <c r="B8" s="3" t="s">
+        <v>211</v>
+      </c>
+      <c r="C8" s="3" t="s">
         <v>246</v>
-      </c>
-    </row>
-    <row r="7" ht="36" spans="1:3">
-      <c r="A7" s="3" t="s">
-        <v>247</v>
-      </c>
-      <c r="B7" s="3" t="s">
-        <v>210</v>
-      </c>
-      <c r="C7" s="3" t="s">
-        <v>248</v>
-      </c>
-    </row>
-    <row r="8" ht="54" spans="1:3">
-      <c r="A8" s="3" t="s">
-        <v>249</v>
-      </c>
-      <c r="B8" s="3" t="s">
-        <v>215</v>
-      </c>
-      <c r="C8" s="3" t="s">
-        <v>250</v>
       </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-  <headerFooter/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
-  <sheetPr/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <dimension ref="A1:C9"/>
-  <sheetFormatPr defaultColWidth="8.88888888888889" defaultRowHeight="18" outlineLevelCol="2"/>
+  <sheetFormatPr defaultColWidth="8.88671875" defaultRowHeight="18"/>
   <cols>
-    <col min="1" max="1" width="17.6666666666667" style="1" customWidth="1"/>
-    <col min="2" max="2" width="33.3333333333333" style="1" customWidth="1"/>
-    <col min="3" max="3" width="63.8888888888889" style="1" customWidth="1"/>
-    <col min="4" max="16384" width="8.88888888888889" style="1"/>
+    <col min="1" max="1" width="17.6640625" style="1" customWidth="1"/>
+    <col min="2" max="2" width="33.33203125" style="1" customWidth="1"/>
+    <col min="3" max="3" width="63.88671875" style="1" customWidth="1"/>
+    <col min="4" max="16384" width="8.88671875" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" s="10" customFormat="1" ht="17.4" spans="1:3">
+    <row r="1" spans="1:3" s="10" customFormat="1" ht="17.399999999999999">
       <c r="A1" s="14" t="s">
         <v>1</v>
       </c>
@@ -2873,24 +2719,22 @@
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-  <headerFooter/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
-  <sheetPr/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
   <dimension ref="A1:C11"/>
-  <sheetFormatPr defaultColWidth="8.88888888888889" defaultRowHeight="18" outlineLevelCol="2"/>
+  <sheetFormatPr defaultColWidth="8.88671875" defaultRowHeight="18"/>
   <cols>
-    <col min="1" max="1" width="33.2222222222222" style="1" customWidth="1"/>
-    <col min="2" max="2" width="31.6666666666667" style="1" customWidth="1"/>
-    <col min="3" max="3" width="93.3333333333333" style="1" customWidth="1"/>
-    <col min="4" max="4" width="80.6666666666667" style="1" customWidth="1"/>
-    <col min="5" max="16384" width="8.88888888888889" style="1"/>
+    <col min="1" max="1" width="33.21875" style="1" customWidth="1"/>
+    <col min="2" max="2" width="31.6640625" style="1" customWidth="1"/>
+    <col min="3" max="3" width="93.33203125" style="1" customWidth="1"/>
+    <col min="4" max="4" width="80.6640625" style="1" customWidth="1"/>
+    <col min="5" max="16384" width="8.88671875" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" s="10" customFormat="1" ht="17.4" spans="1:3">
+    <row r="1" spans="1:3" s="10" customFormat="1" ht="17.399999999999999">
       <c r="A1" s="14" t="s">
         <v>1</v>
       </c>
@@ -3013,23 +2857,21 @@
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-  <headerFooter/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
-  <sheetPr/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0300-000000000000}">
   <dimension ref="A1:C8"/>
-  <sheetFormatPr defaultColWidth="8.88888888888889" defaultRowHeight="18" outlineLevelRow="7" outlineLevelCol="2"/>
+  <sheetFormatPr defaultColWidth="8.88671875" defaultRowHeight="18"/>
   <cols>
     <col min="1" max="1" width="26" style="1" customWidth="1"/>
-    <col min="2" max="2" width="26.4444444444444" style="1" customWidth="1"/>
-    <col min="3" max="3" width="64.5555555555556" style="1" customWidth="1"/>
-    <col min="4" max="16384" width="8.88888888888889" style="1"/>
+    <col min="2" max="2" width="26.44140625" style="1" customWidth="1"/>
+    <col min="3" max="3" width="64.5546875" style="1" customWidth="1"/>
+    <col min="4" max="16384" width="8.88671875" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" ht="18.15" spans="1:3">
+    <row r="1" spans="1:3">
       <c r="A1" s="13" t="s">
         <v>1</v>
       </c>
@@ -3040,7 +2882,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="2" ht="48" customHeight="1" spans="1:3">
+    <row r="2" spans="1:3" ht="48" customHeight="1">
       <c r="A2" s="12" t="s">
         <v>58</v>
       </c>
@@ -3051,7 +2893,7 @@
         <v>60</v>
       </c>
     </row>
-    <row r="3" ht="18.75" spans="1:3">
+    <row r="3" spans="1:3">
       <c r="A3" s="12" t="s">
         <v>61</v>
       </c>
@@ -3062,7 +2904,7 @@
         <v>62</v>
       </c>
     </row>
-    <row r="4" ht="24" customHeight="1" spans="1:3">
+    <row r="4" spans="1:3" ht="24" customHeight="1">
       <c r="A4" s="12" t="s">
         <v>21</v>
       </c>
@@ -3073,7 +2915,7 @@
         <v>63</v>
       </c>
     </row>
-    <row r="5" ht="18.75" spans="1:3">
+    <row r="5" spans="1:3">
       <c r="A5" s="12" t="s">
         <v>4</v>
       </c>
@@ -3084,7 +2926,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="6" ht="37" customHeight="1" spans="1:3">
+    <row r="6" spans="1:3" ht="37.049999999999997" customHeight="1">
       <c r="A6" s="12" t="s">
         <v>65</v>
       </c>
@@ -3095,7 +2937,7 @@
         <v>67</v>
       </c>
     </row>
-    <row r="7" ht="18.75" spans="1:3">
+    <row r="7" spans="1:3">
       <c r="A7" s="12" t="s">
         <v>68</v>
       </c>
@@ -3106,7 +2948,7 @@
         <v>69</v>
       </c>
     </row>
-    <row r="8" ht="48" customHeight="1" spans="1:3">
+    <row r="8" spans="1:3" ht="48" customHeight="1">
       <c r="A8" s="12" t="s">
         <v>70</v>
       </c>
@@ -3119,23 +2961,21 @@
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-  <headerFooter/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
-  <sheetPr/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0400-000000000000}">
   <dimension ref="A1:C23"/>
-  <sheetFormatPr defaultColWidth="8.88888888888889" defaultRowHeight="18" outlineLevelCol="2"/>
+  <sheetFormatPr defaultColWidth="8.88671875" defaultRowHeight="18"/>
   <cols>
-    <col min="1" max="1" width="41.1111111111111" style="1" customWidth="1"/>
-    <col min="2" max="2" width="46.3333333333333" style="1" customWidth="1"/>
-    <col min="3" max="3" width="55.3333333333333" style="1" customWidth="1"/>
-    <col min="4" max="16384" width="8.88888888888889" style="1"/>
+    <col min="1" max="1" width="41.109375" style="1" customWidth="1"/>
+    <col min="2" max="2" width="46.33203125" style="1" customWidth="1"/>
+    <col min="3" max="3" width="55.33203125" style="1" customWidth="1"/>
+    <col min="4" max="16384" width="8.88671875" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" ht="18.15" spans="1:3">
+    <row r="1" spans="1:3">
       <c r="A1" s="13" t="s">
         <v>1</v>
       </c>
@@ -3146,7 +2986,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="2" ht="36.75" spans="1:3">
+    <row r="2" spans="1:3" ht="36">
       <c r="A2" s="12" t="s">
         <v>72</v>
       </c>
@@ -3157,7 +2997,7 @@
         <v>73</v>
       </c>
     </row>
-    <row r="3" ht="18.75" spans="1:3">
+    <row r="3" spans="1:3">
       <c r="A3" s="12" t="s">
         <v>61</v>
       </c>
@@ -3168,7 +3008,7 @@
         <v>74</v>
       </c>
     </row>
-    <row r="4" ht="18.75" spans="1:3">
+    <row r="4" spans="1:3" ht="36">
       <c r="A4" s="12" t="s">
         <v>75</v>
       </c>
@@ -3179,7 +3019,7 @@
         <v>76</v>
       </c>
     </row>
-    <row r="5" ht="36.75" spans="1:3">
+    <row r="5" spans="1:3" ht="36">
       <c r="A5" s="12" t="s">
         <v>77</v>
       </c>
@@ -3190,7 +3030,7 @@
         <v>78</v>
       </c>
     </row>
-    <row r="6" ht="18.75" spans="1:3">
+    <row r="6" spans="1:3">
       <c r="A6" s="12" t="s">
         <v>79</v>
       </c>
@@ -3201,7 +3041,7 @@
         <v>80</v>
       </c>
     </row>
-    <row r="7" ht="36.75" spans="1:3">
+    <row r="7" spans="1:3" ht="36">
       <c r="A7" s="12" t="s">
         <v>81</v>
       </c>
@@ -3212,7 +3052,7 @@
         <v>82</v>
       </c>
     </row>
-    <row r="8" ht="36.75" spans="1:3">
+    <row r="8" spans="1:3" ht="36">
       <c r="A8" s="12" t="s">
         <v>83</v>
       </c>
@@ -3223,7 +3063,7 @@
         <v>84</v>
       </c>
     </row>
-    <row r="9" ht="36.75" spans="1:3">
+    <row r="9" spans="1:3" ht="36">
       <c r="A9" s="12" t="s">
         <v>85</v>
       </c>
@@ -3234,7 +3074,7 @@
         <v>86</v>
       </c>
     </row>
-    <row r="10" ht="36.75" spans="1:3">
+    <row r="10" spans="1:3" ht="36">
       <c r="A10" s="12" t="s">
         <v>87</v>
       </c>
@@ -3245,7 +3085,7 @@
         <v>88</v>
       </c>
     </row>
-    <row r="11" ht="36" spans="1:3">
+    <row r="11" spans="1:3" ht="36">
       <c r="A11" s="12" t="s">
         <v>89</v>
       </c>
@@ -3256,7 +3096,7 @@
         <v>90</v>
       </c>
     </row>
-    <row r="12" ht="36.75" spans="1:3">
+    <row r="12" spans="1:3" ht="36">
       <c r="A12" s="12" t="s">
         <v>91</v>
       </c>
@@ -3267,7 +3107,7 @@
         <v>92</v>
       </c>
     </row>
-    <row r="13" ht="36.75" spans="1:3">
+    <row r="13" spans="1:3" ht="36">
       <c r="A13" s="12" t="s">
         <v>93</v>
       </c>
@@ -3278,7 +3118,7 @@
         <v>94</v>
       </c>
     </row>
-    <row r="14" ht="36.75" spans="1:3">
+    <row r="14" spans="1:3" ht="36">
       <c r="A14" s="12" t="s">
         <v>95</v>
       </c>
@@ -3289,7 +3129,7 @@
         <v>96</v>
       </c>
     </row>
-    <row r="15" ht="18.75" spans="1:3">
+    <row r="15" spans="1:3">
       <c r="A15" s="12" t="s">
         <v>97</v>
       </c>
@@ -3300,7 +3140,7 @@
         <v>98</v>
       </c>
     </row>
-    <row r="16" ht="18.75" spans="1:3">
+    <row r="16" spans="1:3">
       <c r="A16" s="12" t="s">
         <v>99</v>
       </c>
@@ -3311,7 +3151,7 @@
         <v>101</v>
       </c>
     </row>
-    <row r="17" ht="18.75" spans="1:3">
+    <row r="17" spans="1:3">
       <c r="A17" s="12" t="s">
         <v>102</v>
       </c>
@@ -3322,7 +3162,7 @@
         <v>103</v>
       </c>
     </row>
-    <row r="18" ht="18.75" spans="1:3">
+    <row r="18" spans="1:3">
       <c r="A18" s="12" t="s">
         <v>104</v>
       </c>
@@ -3333,7 +3173,7 @@
         <v>105</v>
       </c>
     </row>
-    <row r="19" ht="18.75" spans="1:3">
+    <row r="19" spans="1:3">
       <c r="A19" s="12" t="s">
         <v>106</v>
       </c>
@@ -3344,7 +3184,7 @@
         <v>107</v>
       </c>
     </row>
-    <row r="20" ht="36.75" spans="1:3">
+    <row r="20" spans="1:3" ht="36">
       <c r="A20" s="12" t="s">
         <v>108</v>
       </c>
@@ -3355,7 +3195,7 @@
         <v>109</v>
       </c>
     </row>
-    <row r="21" ht="18.75" spans="1:3">
+    <row r="21" spans="1:3">
       <c r="A21" s="12" t="s">
         <v>9</v>
       </c>
@@ -3366,7 +3206,7 @@
         <v>110</v>
       </c>
     </row>
-    <row r="22" ht="18.75" spans="1:3">
+    <row r="22" spans="1:3">
       <c r="A22" s="12" t="s">
         <v>111</v>
       </c>
@@ -3377,7 +3217,7 @@
         <v>112</v>
       </c>
     </row>
-    <row r="23" ht="18.75" spans="1:3">
+    <row r="23" spans="1:3">
       <c r="A23" s="12" t="s">
         <v>113</v>
       </c>
@@ -3390,23 +3230,21 @@
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-  <headerFooter/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
-  <sheetPr/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0500-000000000000}">
   <dimension ref="A1:C8"/>
-  <sheetFormatPr defaultColWidth="8.88888888888889" defaultRowHeight="18" outlineLevelRow="7" outlineLevelCol="2"/>
+  <sheetFormatPr defaultColWidth="8.88671875" defaultRowHeight="18"/>
   <cols>
-    <col min="1" max="1" width="51.6666666666667" style="1" customWidth="1"/>
-    <col min="2" max="2" width="46.4444444444444" style="1" customWidth="1"/>
-    <col min="3" max="3" width="42.6666666666667" style="1" customWidth="1"/>
-    <col min="4" max="16384" width="8.88888888888889" style="1"/>
+    <col min="1" max="1" width="51.6640625" style="1" customWidth="1"/>
+    <col min="2" max="2" width="46.44140625" style="1" customWidth="1"/>
+    <col min="3" max="3" width="42.6640625" style="1" customWidth="1"/>
+    <col min="4" max="16384" width="8.88671875" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" s="10" customFormat="1" ht="18.15" spans="1:3">
+    <row r="1" spans="1:3" s="10" customFormat="1" ht="17.399999999999999">
       <c r="A1" s="11" t="s">
         <v>1</v>
       </c>
@@ -3417,7 +3255,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="2" ht="72.75" spans="1:3">
+    <row r="2" spans="1:3" ht="90">
       <c r="A2" s="12" t="s">
         <v>115</v>
       </c>
@@ -3428,7 +3266,7 @@
         <v>116</v>
       </c>
     </row>
-    <row r="3" ht="54.75" spans="1:3">
+    <row r="3" spans="1:3" ht="54">
       <c r="A3" s="12" t="s">
         <v>117</v>
       </c>
@@ -3439,7 +3277,7 @@
         <v>119</v>
       </c>
     </row>
-    <row r="4" ht="36.75" spans="1:3">
+    <row r="4" spans="1:3" ht="36">
       <c r="A4" s="12" t="s">
         <v>120</v>
       </c>
@@ -3450,7 +3288,7 @@
         <v>121</v>
       </c>
     </row>
-    <row r="5" ht="36.75" spans="1:3">
+    <row r="5" spans="1:3" ht="36">
       <c r="A5" s="12" t="s">
         <v>122</v>
       </c>
@@ -3461,7 +3299,7 @@
         <v>123</v>
       </c>
     </row>
-    <row r="6" ht="36.75" spans="1:3">
+    <row r="6" spans="1:3" ht="36">
       <c r="A6" s="12" t="s">
         <v>124</v>
       </c>
@@ -3472,7 +3310,7 @@
         <v>125</v>
       </c>
     </row>
-    <row r="7" ht="36.75" spans="1:3">
+    <row r="7" spans="1:3" ht="36">
       <c r="A7" s="12" t="s">
         <v>126</v>
       </c>
@@ -3483,7 +3321,7 @@
         <v>127</v>
       </c>
     </row>
-    <row r="8" ht="54.75" spans="1:3">
+    <row r="8" spans="1:3" ht="54">
       <c r="A8" s="12" t="s">
         <v>128</v>
       </c>
@@ -3496,20 +3334,20 @@
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-  <headerFooter/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
-  <sheetPr/>
-  <dimension ref="A1:C5"/>
-  <sheetFormatPr defaultColWidth="42.3333333333333" defaultRowHeight="18" outlineLevelRow="4" outlineLevelCol="2"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0700-000000000000}">
+  <dimension ref="A1:C18"/>
+  <sheetFormatPr defaultColWidth="8.88671875" defaultRowHeight="14.4"/>
   <cols>
-    <col min="1" max="16384" width="42.3333333333333" style="1" customWidth="1"/>
+    <col min="1" max="1" width="20.5546875" customWidth="1"/>
+    <col min="2" max="2" width="27.109375" customWidth="1"/>
+    <col min="3" max="3" width="47.6640625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" s="6" customFormat="1" spans="1:3">
+    <row r="1" spans="1:3" s="9" customFormat="1" ht="17.399999999999999">
       <c r="A1" s="7" t="s">
         <v>130</v>
       </c>
@@ -3520,284 +3358,258 @@
         <v>3</v>
       </c>
     </row>
-    <row r="2" ht="54" spans="1:3">
+    <row r="2" spans="1:3" ht="54">
       <c r="A2" s="8" t="s">
-        <v>7</v>
+        <v>133</v>
       </c>
       <c r="B2" s="8" t="s">
+        <v>134</v>
+      </c>
+      <c r="C2" s="8" t="s">
+        <v>135</v>
+      </c>
+    </row>
+    <row r="3" spans="1:3" ht="54">
+      <c r="A3" s="8" t="s">
+        <v>21</v>
+      </c>
+      <c r="B3" s="8" t="s">
         <v>131</v>
       </c>
-      <c r="C2" s="8" t="s">
+      <c r="C3" s="8" t="s">
+        <v>136</v>
+      </c>
+    </row>
+    <row r="4" spans="1:3" ht="36">
+      <c r="A4" s="8" t="s">
+        <v>137</v>
+      </c>
+      <c r="B4" s="8" t="s">
+        <v>131</v>
+      </c>
+      <c r="C4" s="8" t="s">
+        <v>138</v>
+      </c>
+    </row>
+    <row r="5" spans="1:3" ht="36">
+      <c r="A5" s="8" t="s">
+        <v>139</v>
+      </c>
+      <c r="B5" s="8" t="s">
+        <v>131</v>
+      </c>
+      <c r="C5" s="8" t="s">
+        <v>140</v>
+      </c>
+    </row>
+    <row r="6" spans="1:3" ht="36">
+      <c r="A6" s="8" t="s">
+        <v>141</v>
+      </c>
+      <c r="B6" s="8" t="s">
+        <v>131</v>
+      </c>
+      <c r="C6" s="8" t="s">
+        <v>142</v>
+      </c>
+    </row>
+    <row r="7" spans="1:3" ht="36">
+      <c r="A7" s="8" t="s">
+        <v>143</v>
+      </c>
+      <c r="B7" s="8" t="s">
+        <v>131</v>
+      </c>
+      <c r="C7" s="8" t="s">
+        <v>144</v>
+      </c>
+    </row>
+    <row r="8" spans="1:3" ht="54">
+      <c r="A8" s="8" t="s">
+        <v>145</v>
+      </c>
+      <c r="B8" s="8" t="s">
+        <v>146</v>
+      </c>
+      <c r="C8" s="8" t="s">
+        <v>147</v>
+      </c>
+    </row>
+    <row r="9" spans="1:3" ht="54">
+      <c r="A9" s="8" t="s">
+        <v>148</v>
+      </c>
+      <c r="B9" s="8" t="s">
+        <v>146</v>
+      </c>
+      <c r="C9" s="8" t="s">
+        <v>149</v>
+      </c>
+    </row>
+    <row r="10" spans="1:3" ht="36">
+      <c r="A10" s="8" t="s">
+        <v>150</v>
+      </c>
+      <c r="B10" s="8" t="s">
+        <v>151</v>
+      </c>
+      <c r="C10" s="8" t="s">
+        <v>152</v>
+      </c>
+    </row>
+    <row r="11" spans="1:3" ht="54">
+      <c r="A11" s="8" t="s">
+        <v>153</v>
+      </c>
+      <c r="B11" s="8" t="s">
+        <v>151</v>
+      </c>
+      <c r="C11" s="8" t="s">
+        <v>154</v>
+      </c>
+    </row>
+    <row r="12" spans="1:3" ht="54">
+      <c r="A12" s="8" t="s">
+        <v>155</v>
+      </c>
+      <c r="B12" s="8" t="s">
+        <v>151</v>
+      </c>
+      <c r="C12" s="8" t="s">
+        <v>156</v>
+      </c>
+    </row>
+    <row r="13" spans="1:3" ht="54">
+      <c r="A13" s="8" t="s">
+        <v>157</v>
+      </c>
+      <c r="B13" s="8" t="s">
+        <v>146</v>
+      </c>
+      <c r="C13" s="8" t="s">
+        <v>158</v>
+      </c>
+    </row>
+    <row r="14" spans="1:3" ht="36">
+      <c r="A14" s="8" t="s">
+        <v>23</v>
+      </c>
+      <c r="B14" s="8" t="s">
         <v>132</v>
       </c>
-    </row>
-    <row r="3" ht="67" customHeight="1" spans="1:3">
-      <c r="A3" s="8" t="s">
-        <v>9</v>
-      </c>
-      <c r="B3" s="8" t="s">
-        <v>133</v>
-      </c>
-      <c r="C3" s="8" t="s">
-        <v>134</v>
-      </c>
-    </row>
-    <row r="4" ht="36" spans="1:3">
-      <c r="A4" s="8" t="s">
-        <v>111</v>
-      </c>
-      <c r="B4" s="8" t="s">
-        <v>133</v>
-      </c>
-      <c r="C4" s="8" t="s">
-        <v>135</v>
-      </c>
-    </row>
-    <row r="5" ht="67" customHeight="1" spans="1:3">
-      <c r="A5" s="8" t="s">
-        <v>113</v>
-      </c>
-      <c r="B5" s="8" t="s">
-        <v>133</v>
-      </c>
-      <c r="C5" s="8" t="s">
-        <v>136</v>
+      <c r="C14" s="8" t="s">
+        <v>159</v>
+      </c>
+    </row>
+    <row r="15" spans="1:3" ht="54">
+      <c r="A15" s="8" t="s">
+        <v>25</v>
+      </c>
+      <c r="B15" s="8" t="s">
+        <v>132</v>
+      </c>
+      <c r="C15" s="8" t="s">
+        <v>160</v>
+      </c>
+    </row>
+    <row r="16" spans="1:3" ht="54">
+      <c r="A16" s="8" t="s">
+        <v>27</v>
+      </c>
+      <c r="B16" s="8" t="s">
+        <v>132</v>
+      </c>
+      <c r="C16" s="8" t="s">
+        <v>161</v>
+      </c>
+    </row>
+    <row r="17" spans="1:3" ht="36">
+      <c r="A17" s="8" t="s">
+        <v>162</v>
+      </c>
+      <c r="B17" s="8" t="s">
+        <v>131</v>
+      </c>
+      <c r="C17" s="8" t="s">
+        <v>163</v>
+      </c>
+    </row>
+    <row r="18" spans="1:3" ht="36">
+      <c r="A18" s="8" t="s">
+        <v>164</v>
+      </c>
+      <c r="B18" s="8" t="s">
+        <v>131</v>
+      </c>
+      <c r="C18" s="8" t="s">
+        <v>165</v>
       </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-  <headerFooter/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
-  <sheetPr/>
-  <dimension ref="A1:C18"/>
-  <sheetFormatPr defaultColWidth="8.88888888888889" defaultRowHeight="14.4" outlineLevelCol="2"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{2EE4F384-0682-4B7B-8DBB-A7CBD3E6E09C}">
+  <dimension ref="A1:C3"/>
+  <sheetFormatPr defaultRowHeight="14.4"/>
   <cols>
-    <col min="1" max="1" width="20.5555555555556" customWidth="1"/>
-    <col min="2" max="2" width="27.1111111111111" customWidth="1"/>
-    <col min="3" max="3" width="47.6666666666667" customWidth="1"/>
+    <col min="1" max="1" width="11.5546875" customWidth="1"/>
+    <col min="2" max="2" width="24.33203125" customWidth="1"/>
+    <col min="3" max="3" width="37" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" s="9" customFormat="1" ht="17.4" spans="1:3">
-      <c r="A1" s="7" t="s">
+    <row r="1" spans="1:3" ht="42" thickBot="1">
+      <c r="A1" s="21" t="s">
         <v>130</v>
       </c>
-      <c r="B1" s="7" t="s">
+      <c r="B1" s="21" t="s">
         <v>2</v>
       </c>
-      <c r="C1" s="7" t="s">
+      <c r="C1" s="21" t="s">
         <v>3</v>
       </c>
     </row>
-    <row r="2" ht="54" spans="1:3">
-      <c r="A2" s="8" t="s">
-        <v>137</v>
-      </c>
-      <c r="B2" s="8" t="s">
-        <v>138</v>
-      </c>
-      <c r="C2" s="8" t="s">
-        <v>139</v>
-      </c>
-    </row>
-    <row r="3" ht="54" spans="1:3">
-      <c r="A3" s="8" t="s">
-        <v>21</v>
-      </c>
-      <c r="B3" s="8" t="s">
-        <v>131</v>
-      </c>
-      <c r="C3" s="8" t="s">
-        <v>140</v>
-      </c>
-    </row>
-    <row r="4" ht="36" spans="1:3">
-      <c r="A4" s="8" t="s">
-        <v>141</v>
-      </c>
-      <c r="B4" s="8" t="s">
-        <v>131</v>
-      </c>
-      <c r="C4" s="8" t="s">
-        <v>142</v>
-      </c>
-    </row>
-    <row r="5" ht="36" spans="1:3">
-      <c r="A5" s="8" t="s">
-        <v>143</v>
-      </c>
-      <c r="B5" s="8" t="s">
-        <v>131</v>
-      </c>
-      <c r="C5" s="8" t="s">
-        <v>144</v>
-      </c>
-    </row>
-    <row r="6" ht="36" spans="1:3">
-      <c r="A6" s="8" t="s">
-        <v>145</v>
-      </c>
-      <c r="B6" s="8" t="s">
-        <v>131</v>
-      </c>
-      <c r="C6" s="8" t="s">
-        <v>146</v>
-      </c>
-    </row>
-    <row r="7" ht="36" spans="1:3">
-      <c r="A7" s="8" t="s">
-        <v>147</v>
-      </c>
-      <c r="B7" s="8" t="s">
-        <v>131</v>
-      </c>
-      <c r="C7" s="8" t="s">
-        <v>148</v>
-      </c>
-    </row>
-    <row r="8" ht="54" spans="1:3">
-      <c r="A8" s="8" t="s">
-        <v>149</v>
-      </c>
-      <c r="B8" s="8" t="s">
-        <v>150</v>
-      </c>
-      <c r="C8" s="8" t="s">
-        <v>151</v>
-      </c>
-    </row>
-    <row r="9" ht="54" spans="1:3">
-      <c r="A9" s="8" t="s">
-        <v>152</v>
-      </c>
-      <c r="B9" s="8" t="s">
-        <v>150</v>
-      </c>
-      <c r="C9" s="8" t="s">
-        <v>153</v>
-      </c>
-    </row>
-    <row r="10" ht="36" spans="1:3">
-      <c r="A10" s="8" t="s">
-        <v>154</v>
-      </c>
-      <c r="B10" s="8" t="s">
-        <v>155</v>
-      </c>
-      <c r="C10" s="8" t="s">
-        <v>156</v>
-      </c>
-    </row>
-    <row r="11" ht="54" spans="1:3">
-      <c r="A11" s="8" t="s">
-        <v>157</v>
-      </c>
-      <c r="B11" s="8" t="s">
-        <v>155</v>
-      </c>
-      <c r="C11" s="8" t="s">
-        <v>158</v>
-      </c>
-    </row>
-    <row r="12" ht="54" spans="1:3">
-      <c r="A12" s="8" t="s">
-        <v>159</v>
-      </c>
-      <c r="B12" s="8" t="s">
-        <v>155</v>
-      </c>
-      <c r="C12" s="8" t="s">
-        <v>160</v>
-      </c>
-    </row>
-    <row r="13" ht="54" spans="1:3">
-      <c r="A13" s="8" t="s">
-        <v>161</v>
-      </c>
-      <c r="B13" s="8" t="s">
-        <v>150</v>
-      </c>
-      <c r="C13" s="8" t="s">
-        <v>162</v>
-      </c>
-    </row>
-    <row r="14" ht="36" spans="1:3">
-      <c r="A14" s="8" t="s">
-        <v>23</v>
-      </c>
-      <c r="B14" s="8" t="s">
-        <v>133</v>
-      </c>
-      <c r="C14" s="8" t="s">
-        <v>163</v>
-      </c>
-    </row>
-    <row r="15" ht="54" spans="1:3">
-      <c r="A15" s="8" t="s">
-        <v>25</v>
-      </c>
-      <c r="B15" s="8" t="s">
-        <v>133</v>
-      </c>
-      <c r="C15" s="8" t="s">
-        <v>164</v>
-      </c>
-    </row>
-    <row r="16" ht="54" spans="1:3">
-      <c r="A16" s="8" t="s">
-        <v>27</v>
-      </c>
-      <c r="B16" s="8" t="s">
-        <v>133</v>
-      </c>
-      <c r="C16" s="8" t="s">
-        <v>165</v>
-      </c>
-    </row>
-    <row r="17" ht="36" spans="1:3">
-      <c r="A17" s="8" t="s">
-        <v>166</v>
-      </c>
-      <c r="B17" s="8" t="s">
-        <v>131</v>
-      </c>
-      <c r="C17" s="8" t="s">
-        <v>167</v>
-      </c>
-    </row>
-    <row r="18" ht="36" spans="1:3">
-      <c r="A18" s="8" t="s">
-        <v>168</v>
-      </c>
-      <c r="B18" s="8" t="s">
-        <v>131</v>
-      </c>
-      <c r="C18" s="8" t="s">
-        <v>169</v>
+    <row r="2" spans="1:3" ht="193.8" thickBot="1">
+      <c r="A2" s="22" t="s">
+        <v>7</v>
+      </c>
+      <c r="B2" s="23" t="s">
+        <v>5</v>
+      </c>
+      <c r="C2" s="23" t="s">
+        <v>262</v>
+      </c>
+    </row>
+    <row r="3" spans="1:3" ht="177.6" thickBot="1">
+      <c r="A3" s="22" t="s">
+        <v>257</v>
+      </c>
+      <c r="B3" s="23" t="s">
+        <v>10</v>
+      </c>
+      <c r="C3" s="23" t="s">
+        <v>263</v>
       </c>
     </row>
   </sheetData>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-  <headerFooter/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
-  <sheetPr/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0800-000000000000}">
   <dimension ref="A1:C18"/>
-  <sheetFormatPr defaultColWidth="8.88888888888889" defaultRowHeight="18" outlineLevelCol="2"/>
+  <sheetFormatPr defaultColWidth="8.88671875" defaultRowHeight="18"/>
   <cols>
-    <col min="1" max="1" width="28.6666666666667" style="1" customWidth="1"/>
-    <col min="2" max="2" width="29.8888888888889" style="1" customWidth="1"/>
-    <col min="3" max="3" width="40.5555555555556" style="1" customWidth="1"/>
-    <col min="4" max="16384" width="8.88888888888889" style="1"/>
+    <col min="1" max="1" width="28.6640625" style="1" customWidth="1"/>
+    <col min="2" max="2" width="29.88671875" style="1" customWidth="1"/>
+    <col min="3" max="3" width="40.5546875" style="1" customWidth="1"/>
+    <col min="4" max="16384" width="8.88671875" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" s="6" customFormat="1" spans="1:3">
+    <row r="1" spans="1:3" s="6" customFormat="1">
       <c r="A1" s="7" t="s">
         <v>130</v>
       </c>
@@ -3808,7 +3620,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="2" ht="54" spans="1:3">
+    <row r="2" spans="1:3" ht="54">
       <c r="A2" s="8" t="s">
         <v>61</v>
       </c>
@@ -3816,21 +3628,21 @@
         <v>131</v>
       </c>
       <c r="C2" s="8" t="s">
-        <v>170</v>
-      </c>
-    </row>
-    <row r="3" ht="36" spans="1:3">
+        <v>166</v>
+      </c>
+    </row>
+    <row r="3" spans="1:3" ht="36">
       <c r="A3" s="8" t="s">
-        <v>171</v>
+        <v>167</v>
       </c>
       <c r="B3" s="8" t="s">
-        <v>138</v>
+        <v>134</v>
       </c>
       <c r="C3" s="8" t="s">
-        <v>172</v>
-      </c>
-    </row>
-    <row r="4" ht="36" spans="1:3">
+        <v>168</v>
+      </c>
+    </row>
+    <row r="4" spans="1:3" ht="36">
       <c r="A4" s="8" t="s">
         <v>4</v>
       </c>
@@ -3838,10 +3650,10 @@
         <v>131</v>
       </c>
       <c r="C4" s="8" t="s">
-        <v>173</v>
-      </c>
-    </row>
-    <row r="5" ht="54" spans="1:3">
+        <v>169</v>
+      </c>
+    </row>
+    <row r="5" spans="1:3" ht="54">
       <c r="A5" s="8" t="s">
         <v>7</v>
       </c>
@@ -3849,154 +3661,153 @@
         <v>131</v>
       </c>
       <c r="C5" s="8" t="s">
-        <v>174</v>
-      </c>
-    </row>
-    <row r="6" ht="54" spans="1:3">
+        <v>170</v>
+      </c>
+    </row>
+    <row r="6" spans="1:3" ht="54">
       <c r="A6" s="8" t="s">
         <v>9</v>
       </c>
       <c r="B6" s="8" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="C6" s="8" t="s">
-        <v>175</v>
-      </c>
-    </row>
-    <row r="7" ht="36" spans="1:3">
+        <v>171</v>
+      </c>
+    </row>
+    <row r="7" spans="1:3" ht="36">
       <c r="A7" s="8" t="s">
         <v>111</v>
       </c>
       <c r="B7" s="8" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="C7" s="8" t="s">
-        <v>176</v>
-      </c>
-    </row>
-    <row r="8" ht="36" spans="1:3">
+        <v>172</v>
+      </c>
+    </row>
+    <row r="8" spans="1:3" ht="36">
       <c r="A8" s="8" t="s">
         <v>113</v>
       </c>
       <c r="B8" s="8" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="C8" s="8" t="s">
+        <v>173</v>
+      </c>
+    </row>
+    <row r="9" spans="1:3" ht="54">
+      <c r="A9" s="8" t="s">
+        <v>174</v>
+      </c>
+      <c r="B9" s="8" t="s">
+        <v>132</v>
+      </c>
+      <c r="C9" s="8" t="s">
+        <v>175</v>
+      </c>
+    </row>
+    <row r="10" spans="1:3" ht="72">
+      <c r="A10" s="8" t="s">
+        <v>176</v>
+      </c>
+      <c r="B10" s="8" t="s">
+        <v>132</v>
+      </c>
+      <c r="C10" s="8" t="s">
         <v>177</v>
       </c>
     </row>
-    <row r="9" ht="54" spans="1:3">
-      <c r="A9" s="8" t="s">
+    <row r="11" spans="1:3" ht="36">
+      <c r="A11" s="8" t="s">
         <v>178</v>
       </c>
-      <c r="B9" s="8" t="s">
-        <v>133</v>
-      </c>
-      <c r="C9" s="8" t="s">
+      <c r="B11" s="8" t="s">
+        <v>132</v>
+      </c>
+      <c r="C11" s="8" t="s">
         <v>179</v>
       </c>
     </row>
-    <row r="10" ht="72" spans="1:3">
-      <c r="A10" s="8" t="s">
+    <row r="12" spans="1:3" ht="90">
+      <c r="A12" s="8" t="s">
         <v>180</v>
       </c>
-      <c r="B10" s="8" t="s">
-        <v>133</v>
-      </c>
-      <c r="C10" s="8" t="s">
+      <c r="B12" s="8" t="s">
+        <v>132</v>
+      </c>
+      <c r="C12" s="8" t="s">
         <v>181</v>
       </c>
     </row>
-    <row r="11" ht="36" spans="1:3">
-      <c r="A11" s="8" t="s">
+    <row r="13" spans="1:3" ht="54">
+      <c r="A13" s="19" t="s">
         <v>182</v>
       </c>
-      <c r="B11" s="8" t="s">
-        <v>133</v>
-      </c>
-      <c r="C11" s="8" t="s">
+      <c r="B13" s="8" t="s">
+        <v>132</v>
+      </c>
+      <c r="C13" s="19" t="s">
         <v>183</v>
       </c>
     </row>
-    <row r="12" ht="90" spans="1:3">
-      <c r="A12" s="8" t="s">
+    <row r="14" spans="1:3" ht="36">
+      <c r="A14" s="19" t="s">
         <v>184</v>
       </c>
-      <c r="B12" s="8" t="s">
-        <v>133</v>
-      </c>
-      <c r="C12" s="8" t="s">
+      <c r="B14" s="8" t="s">
+        <v>132</v>
+      </c>
+      <c r="C14" s="19" t="s">
         <v>185</v>
       </c>
     </row>
-    <row r="13" ht="54" spans="1:3">
-      <c r="A13" s="8" t="s">
+    <row r="15" spans="1:3" ht="36">
+      <c r="A15" s="8" t="s">
         <v>186</v>
       </c>
-      <c r="B13" s="8" t="s">
-        <v>133</v>
-      </c>
-      <c r="C13" s="8" t="s">
+      <c r="B15" s="8" t="s">
+        <v>132</v>
+      </c>
+      <c r="C15" s="8" t="s">
         <v>187</v>
       </c>
     </row>
-    <row r="14" ht="36" spans="1:3">
-      <c r="A14" s="8" t="s">
+    <row r="16" spans="1:3" ht="54">
+      <c r="A16" s="8" t="s">
         <v>188</v>
       </c>
-      <c r="B14" s="8" t="s">
-        <v>133</v>
-      </c>
-      <c r="C14" s="8" t="s">
+      <c r="B16" s="8" t="s">
+        <v>132</v>
+      </c>
+      <c r="C16" s="8" t="s">
         <v>189</v>
       </c>
     </row>
-    <row r="15" ht="36" spans="1:3">
-      <c r="A15" s="8" t="s">
+    <row r="17" spans="1:3" ht="54">
+      <c r="A17" s="19" t="s">
         <v>190</v>
-      </c>
-      <c r="B15" s="8" t="s">
-        <v>133</v>
-      </c>
-      <c r="C15" s="8" t="s">
-        <v>191</v>
-      </c>
-    </row>
-    <row r="16" ht="54" spans="1:3">
-      <c r="A16" s="8" t="s">
-        <v>192</v>
-      </c>
-      <c r="B16" s="8" t="s">
-        <v>133</v>
-      </c>
-      <c r="C16" s="8" t="s">
-        <v>193</v>
-      </c>
-    </row>
-    <row r="17" ht="54" spans="1:3">
-      <c r="A17" s="8" t="s">
-        <v>194</v>
       </c>
       <c r="B17" s="8" t="s">
         <v>131</v>
       </c>
-      <c r="C17" s="8" t="s">
-        <v>195</v>
-      </c>
-    </row>
-    <row r="18" ht="54" spans="1:3">
+      <c r="C17" s="19" t="s">
+        <v>191</v>
+      </c>
+    </row>
+    <row r="18" spans="1:3" ht="72">
       <c r="A18" s="8" t="s">
-        <v>196</v>
+        <v>192</v>
       </c>
       <c r="B18" s="8" t="s">
-        <v>197</v>
+        <v>193</v>
       </c>
       <c r="C18" s="8" t="s">
-        <v>198</v>
+        <v>194</v>
       </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-  <headerFooter/>
 </worksheet>
 </file>
--- a/Data Dictionary.xlsx
+++ b/Data Dictionary.xlsx
@@ -8,30 +8,29 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Đồ_Án_PTDL_Nhóm_2.1\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{57B09C30-91AB-44A7-8904-017A2CC1264C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E31C62F4-B40C-4F61-9654-38E365A8D39A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-96" yWindow="0" windowWidth="11712" windowHeight="13056" firstSheet="6" activeTab="7" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13176" firstSheet="6" activeTab="10" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="Customers.csv" sheetId="1" r:id="rId1"/>
-    <sheet name="edp.json" sheetId="2" r:id="rId2"/>
-    <sheet name="eprom.json" sheetId="3" r:id="rId3"/>
-    <sheet name="reviews.csv" sheetId="4" r:id="rId4"/>
-    <sheet name="shipments_realistic.csv" sheetId="5" r:id="rId5"/>
-    <sheet name="web_traffic.csv &amp; tf.json" sheetId="6" r:id="rId6"/>
-    <sheet name="inventory" sheetId="8" r:id="rId7"/>
-    <sheet name="geography" sheetId="21" r:id="rId8"/>
-    <sheet name="orders_enriched" sheetId="9" r:id="rId9"/>
-    <sheet name="employee" sheetId="15" r:id="rId10"/>
-    <sheet name="order_items" sheetId="10" r:id="rId11"/>
-    <sheet name="customer" sheetId="16" r:id="rId12"/>
-    <sheet name="payment" sheetId="11" r:id="rId13"/>
-    <sheet name="region" sheetId="18" r:id="rId14"/>
-    <sheet name="city" sheetId="19" r:id="rId15"/>
-    <sheet name="district" sheetId="20" r:id="rId16"/>
-    <sheet name="promotions" sheetId="12" r:id="rId17"/>
-    <sheet name="products" sheetId="13" r:id="rId18"/>
-    <sheet name="returns" sheetId="14" r:id="rId19"/>
+    <sheet name="edp.json" sheetId="2" r:id="rId1"/>
+    <sheet name="eprom.json" sheetId="3" r:id="rId2"/>
+    <sheet name="reviews.csv" sheetId="4" r:id="rId3"/>
+    <sheet name="shipments_realistic.csv" sheetId="5" r:id="rId4"/>
+    <sheet name="web_traffic.csv &amp; tf.json" sheetId="6" r:id="rId5"/>
+    <sheet name="inventory" sheetId="8" r:id="rId6"/>
+    <sheet name="geography" sheetId="21" r:id="rId7"/>
+    <sheet name="orders_enriched" sheetId="9" r:id="rId8"/>
+    <sheet name="employee" sheetId="15" r:id="rId9"/>
+    <sheet name="order_items" sheetId="10" r:id="rId10"/>
+    <sheet name="customer" sheetId="16" r:id="rId11"/>
+    <sheet name="payment" sheetId="11" r:id="rId12"/>
+    <sheet name="region" sheetId="18" r:id="rId13"/>
+    <sheet name="city" sheetId="19" r:id="rId14"/>
+    <sheet name="district" sheetId="20" r:id="rId15"/>
+    <sheet name="promotions" sheetId="12" r:id="rId16"/>
+    <sheet name="products" sheetId="13" r:id="rId17"/>
+    <sheet name="returns" sheetId="14" r:id="rId18"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -49,10 +48,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="508" uniqueCount="264">
-  <si>
-    <t>STT</t>
-  </si>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="483" uniqueCount="262">
   <si>
     <t>Tên thuộc tính</t>
   </si>
@@ -82,9 +78,6 @@
   </si>
   <si>
     <t>Chuỗi (String)</t>
-  </si>
-  <si>
-    <t>Tên thành phố nơi khách hàng cư trú.</t>
   </si>
   <si>
     <t>signup_date</t>
@@ -1065,7 +1058,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="24">
+  <cellXfs count="22">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -1113,12 +1106,6 @@
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1">
       <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1">
       <alignment vertical="center"/>
@@ -1617,18 +1604,17 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:D8"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
+  <dimension ref="A1:C9"/>
   <sheetFormatPr defaultColWidth="8.88671875" defaultRowHeight="18"/>
   <cols>
-    <col min="1" max="1" width="6.77734375" style="16" customWidth="1"/>
-    <col min="2" max="2" width="27.88671875" style="1" customWidth="1"/>
-    <col min="3" max="3" width="29.6640625" style="1" customWidth="1"/>
-    <col min="4" max="4" width="66.44140625" style="1" customWidth="1"/>
-    <col min="5" max="16384" width="8.88671875" style="1"/>
+    <col min="1" max="1" width="17.6640625" style="1" customWidth="1"/>
+    <col min="2" max="2" width="33.33203125" style="1" customWidth="1"/>
+    <col min="3" max="3" width="63.88671875" style="1" customWidth="1"/>
+    <col min="4" max="16384" width="8.88671875" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:4" s="10" customFormat="1" ht="17.399999999999999">
+    <row r="1" spans="1:3" s="10" customFormat="1" ht="17.399999999999999">
       <c r="A1" s="14" t="s">
         <v>0</v>
       </c>
@@ -1638,106 +1624,93 @@
       <c r="C1" s="14" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="14" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="2" spans="1:4">
-      <c r="A2" s="17">
-        <v>1</v>
+    </row>
+    <row r="2" spans="1:3">
+      <c r="A2" s="15" t="s">
+        <v>19</v>
       </c>
       <c r="B2" s="15" t="s">
         <v>4</v>
       </c>
       <c r="C2" s="15" t="s">
-        <v>5</v>
-      </c>
-      <c r="D2" s="15" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="3" spans="1:4">
-      <c r="A3" s="17">
-        <v>2</v>
+        <v>20</v>
+      </c>
+    </row>
+    <row r="3" spans="1:3">
+      <c r="A3" s="15" t="s">
+        <v>21</v>
       </c>
       <c r="B3" s="15" t="s">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="C3" s="15" t="s">
-        <v>5</v>
-      </c>
-      <c r="D3" s="15" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="4" spans="1:4">
-      <c r="A4" s="17">
-        <v>3</v>
+        <v>22</v>
+      </c>
+    </row>
+    <row r="4" spans="1:3">
+      <c r="A4" s="15" t="s">
+        <v>23</v>
       </c>
       <c r="B4" s="15" t="s">
         <v>9</v>
       </c>
       <c r="C4" s="15" t="s">
-        <v>10</v>
-      </c>
-      <c r="D4" s="15" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="5" spans="1:4">
-      <c r="A5" s="17">
-        <v>4</v>
+        <v>24</v>
+      </c>
+    </row>
+    <row r="5" spans="1:3">
+      <c r="A5" s="15" t="s">
+        <v>25</v>
       </c>
       <c r="B5" s="15" t="s">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="C5" s="15" t="s">
-        <v>13</v>
-      </c>
-      <c r="D5" s="15" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="6" spans="1:4">
-      <c r="A6" s="17">
-        <v>5</v>
+        <v>26</v>
+      </c>
+    </row>
+    <row r="6" spans="1:3">
+      <c r="A6" s="15" t="s">
+        <v>27</v>
       </c>
       <c r="B6" s="15" t="s">
-        <v>15</v>
+        <v>9</v>
       </c>
       <c r="C6" s="15" t="s">
-        <v>10</v>
-      </c>
-      <c r="D6" s="15" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="7" spans="1:4">
-      <c r="A7" s="17">
-        <v>6</v>
+        <v>28</v>
+      </c>
+    </row>
+    <row r="7" spans="1:3">
+      <c r="A7" s="15" t="s">
+        <v>29</v>
       </c>
       <c r="B7" s="15" t="s">
-        <v>17</v>
+        <v>9</v>
       </c>
       <c r="C7" s="15" t="s">
-        <v>10</v>
-      </c>
-      <c r="D7" s="15" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="8" spans="1:4">
-      <c r="A8" s="17">
-        <v>7</v>
+        <v>30</v>
+      </c>
+    </row>
+    <row r="8" spans="1:3">
+      <c r="A8" s="15" t="s">
+        <v>31</v>
       </c>
       <c r="B8" s="15" t="s">
-        <v>19</v>
+        <v>32</v>
       </c>
       <c r="C8" s="15" t="s">
-        <v>10</v>
-      </c>
-      <c r="D8" s="15" t="s">
-        <v>20</v>
+        <v>33</v>
+      </c>
+    </row>
+    <row r="9" spans="1:3">
+      <c r="A9" s="15" t="s">
+        <v>34</v>
+      </c>
+      <c r="B9" s="15" t="s">
+        <v>32</v>
+      </c>
+      <c r="C9" s="15" t="s">
+        <v>35</v>
       </c>
     </row>
   </sheetData>
@@ -1746,65 +1719,6 @@
 </file>
 
 <file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{61EFBDAE-EAB8-41C5-BB88-AE4529FFB780}">
-  <dimension ref="A1:C4"/>
-  <sheetFormatPr defaultRowHeight="14.4"/>
-  <cols>
-    <col min="1" max="1" width="16.5546875" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="11" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="64.44140625" bestFit="1" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:3">
-      <c r="A1" s="18" t="s">
-        <v>130</v>
-      </c>
-      <c r="B1" s="18" t="s">
-        <v>2</v>
-      </c>
-      <c r="C1" s="18" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="2" spans="1:3">
-      <c r="A2" t="s">
-        <v>182</v>
-      </c>
-      <c r="B2" s="20" t="s">
-        <v>132</v>
-      </c>
-      <c r="C2" t="s">
-        <v>183</v>
-      </c>
-    </row>
-    <row r="3" spans="1:3">
-      <c r="A3" t="s">
-        <v>184</v>
-      </c>
-      <c r="B3" s="20" t="s">
-        <v>132</v>
-      </c>
-      <c r="C3" t="s">
-        <v>185</v>
-      </c>
-    </row>
-    <row r="4" spans="1:3">
-      <c r="A4" t="s">
-        <v>190</v>
-      </c>
-      <c r="B4" s="20" t="s">
-        <v>131</v>
-      </c>
-      <c r="C4" t="s">
-        <v>191</v>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0900-000000000000}">
   <dimension ref="A1:C8"/>
   <sheetFormatPr defaultColWidth="8.88671875" defaultRowHeight="18"/>
@@ -1817,90 +1731,90 @@
   <sheetData>
     <row r="1" spans="1:3" s="6" customFormat="1">
       <c r="A1" s="7" t="s">
-        <v>130</v>
+        <v>128</v>
       </c>
       <c r="B1" s="7" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="7" t="s">
         <v>2</v>
-      </c>
-      <c r="C1" s="7" t="s">
-        <v>3</v>
       </c>
     </row>
     <row r="2" spans="1:3" ht="54">
       <c r="A2" s="8" t="s">
-        <v>61</v>
+        <v>59</v>
       </c>
       <c r="B2" s="8" t="s">
-        <v>131</v>
+        <v>129</v>
       </c>
       <c r="C2" s="8" t="s">
-        <v>195</v>
+        <v>193</v>
       </c>
     </row>
     <row r="3" spans="1:3" ht="54">
       <c r="A3" s="8" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="B3" s="8" t="s">
-        <v>131</v>
+        <v>129</v>
       </c>
       <c r="C3" s="8" t="s">
-        <v>196</v>
+        <v>194</v>
       </c>
     </row>
     <row r="4" spans="1:3" ht="36">
       <c r="A4" s="8" t="s">
-        <v>197</v>
+        <v>195</v>
       </c>
       <c r="B4" s="8" t="s">
-        <v>131</v>
+        <v>129</v>
       </c>
       <c r="C4" s="8" t="s">
-        <v>198</v>
+        <v>196</v>
       </c>
     </row>
     <row r="5" spans="1:3" ht="36">
       <c r="A5" s="8" t="s">
-        <v>199</v>
+        <v>197</v>
       </c>
       <c r="B5" s="8" t="s">
-        <v>146</v>
+        <v>144</v>
       </c>
       <c r="C5" s="8" t="s">
-        <v>200</v>
+        <v>198</v>
       </c>
     </row>
     <row r="6" spans="1:3" ht="54">
       <c r="A6" s="8" t="s">
-        <v>201</v>
+        <v>199</v>
       </c>
       <c r="B6" s="8" t="s">
-        <v>146</v>
+        <v>144</v>
       </c>
       <c r="C6" s="8" t="s">
-        <v>202</v>
+        <v>200</v>
       </c>
     </row>
     <row r="7" spans="1:3" ht="72">
       <c r="A7" s="8" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="B7" s="8" t="s">
-        <v>193</v>
+        <v>191</v>
       </c>
       <c r="C7" s="8" t="s">
-        <v>203</v>
+        <v>201</v>
       </c>
     </row>
     <row r="8" spans="1:3" ht="72">
       <c r="A8" s="8" t="s">
-        <v>204</v>
+        <v>202</v>
       </c>
       <c r="B8" s="8" t="s">
-        <v>193</v>
+        <v>191</v>
       </c>
       <c r="C8" s="8" t="s">
-        <v>205</v>
+        <v>203</v>
       </c>
     </row>
   </sheetData>
@@ -1908,7 +1822,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D95C202C-0552-40EC-83B4-6358B4060693}">
   <dimension ref="A1:C7"/>
   <sheetFormatPr defaultRowHeight="14.4"/>
@@ -1918,81 +1832,81 @@
     <col min="3" max="3" width="24.44140625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" ht="42" thickBot="1">
-      <c r="A1" s="21" t="s">
-        <v>130</v>
-      </c>
-      <c r="B1" s="21" t="s">
+    <row r="1" spans="1:3" ht="15" thickBot="1">
+      <c r="A1" s="19" t="s">
+        <v>128</v>
+      </c>
+      <c r="B1" s="19" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="19" t="s">
         <v>2</v>
       </c>
-      <c r="C1" s="21" t="s">
+    </row>
+    <row r="2" spans="1:3" ht="42" thickBot="1">
+      <c r="A2" s="20" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="2" spans="1:3" ht="124.8" thickBot="1">
-      <c r="A2" s="22" t="s">
+      <c r="B2" s="21" t="s">
         <v>4</v>
       </c>
-      <c r="B2" s="23" t="s">
+      <c r="C2" s="21" t="s">
         <v>5</v>
       </c>
-      <c r="C2" s="23" t="s">
+    </row>
+    <row r="3" spans="1:3" ht="28.2" thickBot="1">
+      <c r="A3" s="20" t="s">
+        <v>10</v>
+      </c>
+      <c r="B3" s="21" t="s">
+        <v>245</v>
+      </c>
+      <c r="C3" s="21" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="4" spans="1:3" ht="28.2" thickBot="1">
+      <c r="A4" s="20" t="s">
+        <v>13</v>
+      </c>
+      <c r="B4" s="21" t="s">
+        <v>9</v>
+      </c>
+      <c r="C4" s="21" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="5" spans="1:3" ht="28.2" thickBot="1">
+      <c r="A5" s="20" t="s">
+        <v>15</v>
+      </c>
+      <c r="B5" s="21" t="s">
+        <v>9</v>
+      </c>
+      <c r="C5" s="21" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="6" spans="1:3" ht="28.2" thickBot="1">
+      <c r="A6" s="20" t="s">
+        <v>17</v>
+      </c>
+      <c r="B6" s="21" t="s">
+        <v>9</v>
+      </c>
+      <c r="C6" s="21" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="7" spans="1:3" ht="42" thickBot="1">
+      <c r="A7" s="20" t="s">
         <v>6</v>
       </c>
-    </row>
-    <row r="3" spans="1:3" ht="111" thickBot="1">
-      <c r="A3" s="22" t="s">
-        <v>12</v>
-      </c>
-      <c r="B3" s="23" t="s">
-        <v>247</v>
-      </c>
-      <c r="C3" s="23" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="4" spans="1:3" ht="69.599999999999994" thickBot="1">
-      <c r="A4" s="22" t="s">
-        <v>15</v>
-      </c>
-      <c r="B4" s="23" t="s">
-        <v>10</v>
-      </c>
-      <c r="C4" s="23" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="5" spans="1:3" ht="69.599999999999994" thickBot="1">
-      <c r="A5" s="22" t="s">
-        <v>17</v>
-      </c>
-      <c r="B5" s="23" t="s">
-        <v>10</v>
-      </c>
-      <c r="C5" s="23" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="6" spans="1:3" ht="111" thickBot="1">
-      <c r="A6" s="22" t="s">
-        <v>19</v>
-      </c>
-      <c r="B6" s="23" t="s">
-        <v>10</v>
-      </c>
-      <c r="C6" s="23" t="s">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="7" spans="1:3" ht="166.2" thickBot="1">
-      <c r="A7" s="22" t="s">
+      <c r="B7" s="21" t="s">
+        <v>4</v>
+      </c>
+      <c r="C7" s="21" t="s">
         <v>7</v>
-      </c>
-      <c r="B7" s="23" t="s">
-        <v>5</v>
-      </c>
-      <c r="C7" s="23" t="s">
-        <v>8</v>
       </c>
     </row>
   </sheetData>
@@ -2000,7 +1914,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0A00-000000000000}">
   <dimension ref="A1:C8"/>
   <sheetFormatPr defaultColWidth="8.88671875" defaultRowHeight="18"/>
@@ -2013,57 +1927,57 @@
   <sheetData>
     <row r="1" spans="1:3">
       <c r="A1" s="4" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="4" t="s">
         <v>1</v>
       </c>
-      <c r="B1" s="4" t="s">
+      <c r="C1" s="4" t="s">
         <v>2</v>
-      </c>
-      <c r="C1" s="4" t="s">
-        <v>3</v>
       </c>
     </row>
     <row r="2" spans="1:3" ht="54">
       <c r="A2" s="5" t="s">
-        <v>61</v>
+        <v>59</v>
       </c>
       <c r="B2" s="5" t="s">
-        <v>206</v>
+        <v>204</v>
       </c>
       <c r="C2" s="5" t="s">
-        <v>207</v>
+        <v>205</v>
       </c>
     </row>
     <row r="3" spans="1:3" ht="90">
       <c r="A3" s="5" t="s">
-        <v>176</v>
+        <v>174</v>
       </c>
       <c r="B3" s="5" t="s">
-        <v>208</v>
+        <v>206</v>
       </c>
       <c r="C3" s="5" t="s">
-        <v>209</v>
+        <v>207</v>
       </c>
     </row>
     <row r="4" spans="1:3" ht="54">
       <c r="A4" s="5" t="s">
+        <v>208</v>
+      </c>
+      <c r="B4" s="5" t="s">
+        <v>209</v>
+      </c>
+      <c r="C4" s="5" t="s">
         <v>210</v>
-      </c>
-      <c r="B4" s="5" t="s">
-        <v>211</v>
-      </c>
-      <c r="C4" s="5" t="s">
-        <v>212</v>
       </c>
     </row>
     <row r="5" spans="1:3" ht="36">
       <c r="A5" s="5" t="s">
-        <v>213</v>
+        <v>211</v>
       </c>
       <c r="B5" s="5" t="s">
-        <v>206</v>
+        <v>204</v>
       </c>
       <c r="C5" s="5" t="s">
-        <v>214</v>
+        <v>212</v>
       </c>
     </row>
     <row r="6" spans="1:3">
@@ -2086,7 +2000,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet14.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1456BB1E-F52F-40CF-B18F-4C959AB21721}">
   <dimension ref="A1:C3"/>
   <sheetFormatPr defaultRowHeight="14.4"/>
@@ -2095,37 +2009,37 @@
     <col min="3" max="3" width="36.109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" ht="42" thickBot="1">
-      <c r="A1" s="21" t="s">
-        <v>130</v>
-      </c>
-      <c r="B1" s="21" t="s">
+    <row r="1" spans="1:3" ht="15" thickBot="1">
+      <c r="A1" s="19" t="s">
+        <v>128</v>
+      </c>
+      <c r="B1" s="19" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="19" t="s">
         <v>2</v>
       </c>
-      <c r="C1" s="21" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="2" spans="1:3" ht="166.2" thickBot="1">
-      <c r="A2" s="22" t="s">
+    </row>
+    <row r="2" spans="1:3" ht="28.2" thickBot="1">
+      <c r="A2" s="20" t="s">
+        <v>246</v>
+      </c>
+      <c r="B2" s="21" t="s">
+        <v>9</v>
+      </c>
+      <c r="C2" s="21" t="s">
+        <v>247</v>
+      </c>
+    </row>
+    <row r="3" spans="1:3" ht="28.2" thickBot="1">
+      <c r="A3" s="20" t="s">
         <v>248</v>
       </c>
-      <c r="B2" s="23" t="s">
-        <v>10</v>
-      </c>
-      <c r="C2" s="23" t="s">
+      <c r="B3" s="21" t="s">
+        <v>9</v>
+      </c>
+      <c r="C3" s="21" t="s">
         <v>249</v>
-      </c>
-    </row>
-    <row r="3" spans="1:3" ht="166.2" thickBot="1">
-      <c r="A3" s="22" t="s">
-        <v>250</v>
-      </c>
-      <c r="B3" s="23" t="s">
-        <v>10</v>
-      </c>
-      <c r="C3" s="23" t="s">
-        <v>251</v>
       </c>
     </row>
   </sheetData>
@@ -2133,7 +2047,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet15.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet14.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{AEC1F8BA-98B3-46C3-8F38-171796BF0C73}">
   <dimension ref="A1:C4"/>
   <sheetFormatPr defaultRowHeight="14.4"/>
@@ -2143,48 +2057,48 @@
     <col min="3" max="3" width="35" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" ht="42" thickBot="1">
-      <c r="A1" s="21" t="s">
-        <v>130</v>
-      </c>
-      <c r="B1" s="21" t="s">
+    <row r="1" spans="1:3" ht="15" thickBot="1">
+      <c r="A1" s="19" t="s">
+        <v>128</v>
+      </c>
+      <c r="B1" s="19" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="19" t="s">
         <v>2</v>
       </c>
-      <c r="C1" s="21" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="2" spans="1:3" ht="207.6" thickBot="1">
-      <c r="A2" s="22" t="s">
+    </row>
+    <row r="2" spans="1:3" ht="42" thickBot="1">
+      <c r="A2" s="20" t="s">
+        <v>250</v>
+      </c>
+      <c r="B2" s="21" t="s">
+        <v>9</v>
+      </c>
+      <c r="C2" s="21" t="s">
+        <v>251</v>
+      </c>
+    </row>
+    <row r="3" spans="1:3" ht="28.2" thickBot="1">
+      <c r="A3" s="20" t="s">
         <v>252</v>
       </c>
-      <c r="B2" s="23" t="s">
-        <v>10</v>
-      </c>
-      <c r="C2" s="23" t="s">
+      <c r="B3" s="21" t="s">
+        <v>9</v>
+      </c>
+      <c r="C3" s="21" t="s">
         <v>253</v>
       </c>
     </row>
-    <row r="3" spans="1:3" ht="124.8" thickBot="1">
-      <c r="A3" s="22" t="s">
+    <row r="4" spans="1:3" ht="28.2" thickBot="1">
+      <c r="A4" s="20" t="s">
+        <v>246</v>
+      </c>
+      <c r="B4" s="21" t="s">
+        <v>9</v>
+      </c>
+      <c r="C4" s="21" t="s">
         <v>254</v>
-      </c>
-      <c r="B3" s="23" t="s">
-        <v>10</v>
-      </c>
-      <c r="C3" s="23" t="s">
-        <v>255</v>
-      </c>
-    </row>
-    <row r="4" spans="1:3" ht="150" thickBot="1">
-      <c r="A4" s="22" t="s">
-        <v>248</v>
-      </c>
-      <c r="B4" s="23" t="s">
-        <v>10</v>
-      </c>
-      <c r="C4" s="23" t="s">
-        <v>256</v>
       </c>
     </row>
   </sheetData>
@@ -2192,7 +2106,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet16.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet15.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{0DC09820-A76E-48BA-B097-1044F967E90C}">
   <dimension ref="A1:C4"/>
   <sheetFormatPr defaultRowHeight="14.4"/>
@@ -2202,48 +2116,48 @@
     <col min="3" max="3" width="26.109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" ht="42" thickBot="1">
-      <c r="A1" s="21" t="s">
-        <v>130</v>
-      </c>
-      <c r="B1" s="21" t="s">
+    <row r="1" spans="1:3" ht="15" thickBot="1">
+      <c r="A1" s="19" t="s">
+        <v>128</v>
+      </c>
+      <c r="B1" s="19" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="19" t="s">
         <v>2</v>
       </c>
-      <c r="C1" s="21" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="2" spans="1:3" ht="166.2" thickBot="1">
-      <c r="A2" s="22" t="s">
+    </row>
+    <row r="2" spans="1:3" ht="42" thickBot="1">
+      <c r="A2" s="20" t="s">
+        <v>255</v>
+      </c>
+      <c r="B2" s="21" t="s">
+        <v>9</v>
+      </c>
+      <c r="C2" s="21" t="s">
+        <v>256</v>
+      </c>
+    </row>
+    <row r="3" spans="1:3" ht="42" thickBot="1">
+      <c r="A3" s="20" t="s">
         <v>257</v>
       </c>
-      <c r="B2" s="23" t="s">
-        <v>10</v>
-      </c>
-      <c r="C2" s="23" t="s">
+      <c r="B3" s="21" t="s">
+        <v>9</v>
+      </c>
+      <c r="C3" s="21" t="s">
         <v>258</v>
       </c>
     </row>
-    <row r="3" spans="1:3" ht="138.6" thickBot="1">
-      <c r="A3" s="22" t="s">
+    <row r="4" spans="1:3" ht="42" thickBot="1">
+      <c r="A4" s="20" t="s">
+        <v>250</v>
+      </c>
+      <c r="B4" s="21" t="s">
+        <v>9</v>
+      </c>
+      <c r="C4" s="21" t="s">
         <v>259</v>
-      </c>
-      <c r="B3" s="23" t="s">
-        <v>10</v>
-      </c>
-      <c r="C3" s="23" t="s">
-        <v>260</v>
-      </c>
-    </row>
-    <row r="4" spans="1:3" ht="138.6" thickBot="1">
-      <c r="A4" s="22" t="s">
-        <v>252</v>
-      </c>
-      <c r="B4" s="23" t="s">
-        <v>10</v>
-      </c>
-      <c r="C4" s="23" t="s">
-        <v>261</v>
       </c>
     </row>
   </sheetData>
@@ -2251,7 +2165,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet17.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet16.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0B00-000000000000}">
   <dimension ref="A1:C11"/>
   <sheetFormatPr defaultColWidth="8.88671875" defaultRowHeight="18"/>
@@ -2264,123 +2178,123 @@
   <sheetData>
     <row r="1" spans="1:3">
       <c r="A1" s="2" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="B1" s="2" t="s">
+      <c r="C1" s="2" t="s">
         <v>2</v>
-      </c>
-      <c r="C1" s="2" t="s">
-        <v>3</v>
       </c>
     </row>
     <row r="2" spans="1:3" ht="36">
       <c r="A2" s="3" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="B2" s="3" t="s">
-        <v>208</v>
+        <v>206</v>
       </c>
       <c r="C2" s="3" t="s">
-        <v>215</v>
+        <v>213</v>
       </c>
     </row>
     <row r="3" spans="1:3" ht="36">
       <c r="A3" s="3" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="B3" s="3" t="s">
-        <v>208</v>
+        <v>206</v>
       </c>
       <c r="C3" s="3" t="s">
-        <v>216</v>
+        <v>214</v>
       </c>
     </row>
     <row r="4" spans="1:3" ht="54">
       <c r="A4" s="3" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="B4" s="3" t="s">
-        <v>208</v>
+        <v>206</v>
       </c>
       <c r="C4" s="3" t="s">
-        <v>217</v>
+        <v>215</v>
       </c>
     </row>
     <row r="5" spans="1:3" ht="36">
       <c r="A5" s="3" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="B5" s="3" t="s">
-        <v>211</v>
+        <v>209</v>
       </c>
       <c r="C5" s="3" t="s">
-        <v>218</v>
+        <v>216</v>
       </c>
     </row>
     <row r="6" spans="1:3" ht="36">
       <c r="A6" s="3" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="B6" s="3" t="s">
-        <v>219</v>
+        <v>217</v>
       </c>
       <c r="C6" s="3" t="s">
-        <v>220</v>
+        <v>218</v>
       </c>
     </row>
     <row r="7" spans="1:3" ht="36">
       <c r="A7" s="3" t="s">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="B7" s="3" t="s">
+        <v>217</v>
+      </c>
+      <c r="C7" s="3" t="s">
         <v>219</v>
-      </c>
-      <c r="C7" s="3" t="s">
-        <v>221</v>
       </c>
     </row>
     <row r="8" spans="1:3" ht="54">
       <c r="A8" s="3" t="s">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="B8" s="3" t="s">
-        <v>208</v>
+        <v>206</v>
       </c>
       <c r="C8" s="3" t="s">
-        <v>222</v>
+        <v>220</v>
       </c>
     </row>
     <row r="9" spans="1:3" ht="54">
       <c r="A9" s="3" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="B9" s="3" t="s">
-        <v>208</v>
+        <v>206</v>
       </c>
       <c r="C9" s="3" t="s">
-        <v>223</v>
+        <v>221</v>
       </c>
     </row>
     <row r="10" spans="1:3" ht="54">
       <c r="A10" s="3" t="s">
-        <v>54</v>
+        <v>52</v>
       </c>
       <c r="B10" s="3" t="s">
-        <v>224</v>
+        <v>222</v>
       </c>
       <c r="C10" s="3" t="s">
-        <v>225</v>
+        <v>223</v>
       </c>
     </row>
     <row r="11" spans="1:3" ht="54">
       <c r="A11" s="3" t="s">
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="B11" s="3" t="s">
-        <v>206</v>
+        <v>204</v>
       </c>
       <c r="C11" s="3" t="s">
-        <v>226</v>
+        <v>224</v>
       </c>
     </row>
   </sheetData>
@@ -2388,7 +2302,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet18.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet17.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0C00-000000000000}">
   <dimension ref="A1:C9"/>
   <sheetFormatPr defaultColWidth="8.88671875" defaultRowHeight="18"/>
@@ -2401,101 +2315,101 @@
   <sheetData>
     <row r="1" spans="1:3">
       <c r="A1" s="2" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="B1" s="2" t="s">
+      <c r="C1" s="2" t="s">
         <v>2</v>
-      </c>
-      <c r="C1" s="2" t="s">
-        <v>3</v>
       </c>
     </row>
     <row r="2" spans="1:3">
       <c r="A2" s="3" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="B2" s="3" t="s">
-        <v>206</v>
+        <v>204</v>
       </c>
       <c r="C2" s="3" t="s">
-        <v>227</v>
+        <v>225</v>
       </c>
     </row>
     <row r="3" spans="1:3" ht="36">
       <c r="A3" s="3" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="B3" s="3" t="s">
-        <v>208</v>
+        <v>206</v>
       </c>
       <c r="C3" s="3" t="s">
-        <v>228</v>
+        <v>226</v>
       </c>
     </row>
     <row r="4" spans="1:3" ht="36">
       <c r="A4" s="3" t="s">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="B4" s="3" t="s">
-        <v>208</v>
+        <v>206</v>
       </c>
       <c r="C4" s="3" t="s">
-        <v>229</v>
+        <v>227</v>
       </c>
     </row>
     <row r="5" spans="1:3" ht="54">
       <c r="A5" s="3" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="B5" s="3" t="s">
-        <v>208</v>
+        <v>206</v>
       </c>
       <c r="C5" s="3" t="s">
-        <v>230</v>
+        <v>228</v>
       </c>
     </row>
     <row r="6" spans="1:3">
       <c r="A6" s="3" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="B6" s="3" t="s">
-        <v>208</v>
+        <v>206</v>
       </c>
       <c r="C6" s="3" t="s">
-        <v>231</v>
+        <v>229</v>
       </c>
     </row>
     <row r="7" spans="1:3" ht="36">
       <c r="A7" s="3" t="s">
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="B7" s="3" t="s">
-        <v>208</v>
+        <v>206</v>
       </c>
       <c r="C7" s="3" t="s">
-        <v>232</v>
+        <v>230</v>
       </c>
     </row>
     <row r="8" spans="1:3" ht="36">
       <c r="A8" s="3" t="s">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="B8" s="3" t="s">
-        <v>211</v>
+        <v>209</v>
       </c>
       <c r="C8" s="3" t="s">
-        <v>233</v>
+        <v>231</v>
       </c>
     </row>
     <row r="9" spans="1:3" ht="36">
       <c r="A9" s="3" t="s">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="B9" s="3" t="s">
-        <v>211</v>
+        <v>209</v>
       </c>
       <c r="C9" s="3" t="s">
-        <v>234</v>
+        <v>232</v>
       </c>
     </row>
   </sheetData>
@@ -2503,7 +2417,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet19.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet18.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0D00-000000000000}">
   <dimension ref="A1:C8"/>
   <sheetFormatPr defaultColWidth="8.88671875" defaultRowHeight="18"/>
@@ -2516,90 +2430,90 @@
   <sheetData>
     <row r="1" spans="1:3">
       <c r="A1" s="2" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="B1" s="2" t="s">
+      <c r="C1" s="2" t="s">
         <v>2</v>
-      </c>
-      <c r="C1" s="2" t="s">
-        <v>3</v>
       </c>
     </row>
     <row r="2" spans="1:3" ht="36">
       <c r="A2" s="3" t="s">
-        <v>235</v>
+        <v>233</v>
       </c>
       <c r="B2" s="3" t="s">
-        <v>208</v>
+        <v>206</v>
       </c>
       <c r="C2" s="3" t="s">
-        <v>236</v>
+        <v>234</v>
       </c>
     </row>
     <row r="3" spans="1:3" ht="54">
       <c r="A3" s="3" t="s">
-        <v>61</v>
+        <v>59</v>
       </c>
       <c r="B3" s="3" t="s">
-        <v>206</v>
+        <v>204</v>
       </c>
       <c r="C3" s="3" t="s">
-        <v>237</v>
+        <v>235</v>
       </c>
     </row>
     <row r="4" spans="1:3" ht="36">
       <c r="A4" s="3" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="B4" s="3" t="s">
-        <v>206</v>
+        <v>204</v>
       </c>
       <c r="C4" s="3" t="s">
-        <v>238</v>
+        <v>236</v>
       </c>
     </row>
     <row r="5" spans="1:3" ht="54">
       <c r="A5" s="3" t="s">
-        <v>239</v>
+        <v>237</v>
       </c>
       <c r="B5" s="3" t="s">
-        <v>219</v>
+        <v>217</v>
       </c>
       <c r="C5" s="3" t="s">
-        <v>240</v>
+        <v>238</v>
       </c>
     </row>
     <row r="6" spans="1:3" ht="108">
       <c r="A6" s="3" t="s">
-        <v>241</v>
+        <v>239</v>
       </c>
       <c r="B6" s="3" t="s">
-        <v>208</v>
+        <v>206</v>
       </c>
       <c r="C6" s="3" t="s">
-        <v>242</v>
+        <v>240</v>
       </c>
     </row>
     <row r="7" spans="1:3" ht="36">
       <c r="A7" s="3" t="s">
-        <v>243</v>
+        <v>241</v>
       </c>
       <c r="B7" s="3" t="s">
-        <v>206</v>
+        <v>204</v>
       </c>
       <c r="C7" s="3" t="s">
-        <v>244</v>
+        <v>242</v>
       </c>
     </row>
     <row r="8" spans="1:3" ht="54">
       <c r="A8" s="3" t="s">
-        <v>245</v>
+        <v>243</v>
       </c>
       <c r="B8" s="3" t="s">
-        <v>211</v>
+        <v>209</v>
       </c>
       <c r="C8" s="3" t="s">
-        <v>246</v>
+        <v>244</v>
       </c>
     </row>
   </sheetData>
@@ -2608,121 +2522,6 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
-  <dimension ref="A1:C9"/>
-  <sheetFormatPr defaultColWidth="8.88671875" defaultRowHeight="18"/>
-  <cols>
-    <col min="1" max="1" width="17.6640625" style="1" customWidth="1"/>
-    <col min="2" max="2" width="33.33203125" style="1" customWidth="1"/>
-    <col min="3" max="3" width="63.88671875" style="1" customWidth="1"/>
-    <col min="4" max="16384" width="8.88671875" style="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:3" s="10" customFormat="1" ht="17.399999999999999">
-      <c r="A1" s="14" t="s">
-        <v>1</v>
-      </c>
-      <c r="B1" s="14" t="s">
-        <v>2</v>
-      </c>
-      <c r="C1" s="14" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="2" spans="1:3">
-      <c r="A2" s="15" t="s">
-        <v>21</v>
-      </c>
-      <c r="B2" s="15" t="s">
-        <v>5</v>
-      </c>
-      <c r="C2" s="15" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="3" spans="1:3">
-      <c r="A3" s="15" t="s">
-        <v>23</v>
-      </c>
-      <c r="B3" s="15" t="s">
-        <v>10</v>
-      </c>
-      <c r="C3" s="15" t="s">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="4" spans="1:3">
-      <c r="A4" s="15" t="s">
-        <v>25</v>
-      </c>
-      <c r="B4" s="15" t="s">
-        <v>10</v>
-      </c>
-      <c r="C4" s="15" t="s">
-        <v>26</v>
-      </c>
-    </row>
-    <row r="5" spans="1:3">
-      <c r="A5" s="15" t="s">
-        <v>27</v>
-      </c>
-      <c r="B5" s="15" t="s">
-        <v>10</v>
-      </c>
-      <c r="C5" s="15" t="s">
-        <v>28</v>
-      </c>
-    </row>
-    <row r="6" spans="1:3">
-      <c r="A6" s="15" t="s">
-        <v>29</v>
-      </c>
-      <c r="B6" s="15" t="s">
-        <v>10</v>
-      </c>
-      <c r="C6" s="15" t="s">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="7" spans="1:3">
-      <c r="A7" s="15" t="s">
-        <v>31</v>
-      </c>
-      <c r="B7" s="15" t="s">
-        <v>10</v>
-      </c>
-      <c r="C7" s="15" t="s">
-        <v>32</v>
-      </c>
-    </row>
-    <row r="8" spans="1:3">
-      <c r="A8" s="15" t="s">
-        <v>33</v>
-      </c>
-      <c r="B8" s="15" t="s">
-        <v>34</v>
-      </c>
-      <c r="C8" s="15" t="s">
-        <v>35</v>
-      </c>
-    </row>
-    <row r="9" spans="1:3">
-      <c r="A9" s="15" t="s">
-        <v>36</v>
-      </c>
-      <c r="B9" s="15" t="s">
-        <v>34</v>
-      </c>
-      <c r="C9" s="15" t="s">
-        <v>37</v>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
   <dimension ref="A1:C11"/>
   <sheetFormatPr defaultColWidth="8.88671875" defaultRowHeight="18"/>
@@ -2736,123 +2535,123 @@
   <sheetData>
     <row r="1" spans="1:3" s="10" customFormat="1" ht="17.399999999999999">
       <c r="A1" s="14" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="14" t="s">
         <v>1</v>
       </c>
-      <c r="B1" s="14" t="s">
+      <c r="C1" s="14" t="s">
         <v>2</v>
-      </c>
-      <c r="C1" s="14" t="s">
-        <v>3</v>
       </c>
     </row>
     <row r="2" spans="1:3">
       <c r="A2" s="15" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="B2" s="15" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="C2" s="15" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
     </row>
     <row r="3" spans="1:3">
       <c r="A3" s="15" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="B3" s="15" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="C3" s="15" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
     </row>
     <row r="4" spans="1:3">
       <c r="A4" s="15" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="B4" s="15" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="C4" s="15" t="s">
-        <v>43</v>
+        <v>41</v>
       </c>
     </row>
     <row r="5" spans="1:3">
       <c r="A5" s="15" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="B5" s="15" t="s">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="C5" s="15" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
     </row>
     <row r="6" spans="1:3">
       <c r="A6" s="15" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="B6" s="15" t="s">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="C6" s="15" t="s">
-        <v>47</v>
+        <v>45</v>
       </c>
     </row>
     <row r="7" spans="1:3">
       <c r="A7" s="15" t="s">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="B7" s="15" t="s">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="C7" s="15" t="s">
-        <v>49</v>
+        <v>47</v>
       </c>
     </row>
     <row r="8" spans="1:3">
       <c r="A8" s="15" t="s">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="B8" s="15" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="C8" s="15" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
     </row>
     <row r="9" spans="1:3">
       <c r="A9" s="15" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="B9" s="15" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="C9" s="15" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
     </row>
     <row r="10" spans="1:3">
       <c r="A10" s="15" t="s">
-        <v>54</v>
+        <v>52</v>
       </c>
       <c r="B10" s="15" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C10" s="15" t="s">
-        <v>55</v>
+        <v>53</v>
       </c>
     </row>
     <row r="11" spans="1:3">
       <c r="A11" s="15" t="s">
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="B11" s="15" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C11" s="15" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
     </row>
   </sheetData>
@@ -2860,7 +2659,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0300-000000000000}">
   <dimension ref="A1:C8"/>
   <sheetFormatPr defaultColWidth="8.88671875" defaultRowHeight="18"/>
@@ -2873,90 +2672,90 @@
   <sheetData>
     <row r="1" spans="1:3">
       <c r="A1" s="13" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="13" t="s">
         <v>1</v>
       </c>
-      <c r="B1" s="13" t="s">
+      <c r="C1" s="13" t="s">
         <v>2</v>
-      </c>
-      <c r="C1" s="13" t="s">
-        <v>3</v>
       </c>
     </row>
     <row r="2" spans="1:3" ht="48" customHeight="1">
       <c r="A2" s="12" t="s">
+        <v>56</v>
+      </c>
+      <c r="B2" s="12" t="s">
+        <v>57</v>
+      </c>
+      <c r="C2" s="12" t="s">
         <v>58</v>
-      </c>
-      <c r="B2" s="12" t="s">
-        <v>59</v>
-      </c>
-      <c r="C2" s="12" t="s">
-        <v>60</v>
       </c>
     </row>
     <row r="3" spans="1:3">
       <c r="A3" s="12" t="s">
-        <v>61</v>
+        <v>59</v>
       </c>
       <c r="B3" s="12" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C3" s="12" t="s">
-        <v>62</v>
+        <v>60</v>
       </c>
     </row>
     <row r="4" spans="1:3" ht="24" customHeight="1">
       <c r="A4" s="12" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="B4" s="12" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C4" s="12" t="s">
-        <v>63</v>
+        <v>61</v>
       </c>
     </row>
     <row r="5" spans="1:3">
       <c r="A5" s="12" t="s">
+        <v>3</v>
+      </c>
+      <c r="B5" s="12" t="s">
         <v>4</v>
       </c>
-      <c r="B5" s="12" t="s">
-        <v>5</v>
-      </c>
       <c r="C5" s="12" t="s">
-        <v>64</v>
+        <v>62</v>
       </c>
     </row>
     <row r="6" spans="1:3" ht="37.049999999999997" customHeight="1">
       <c r="A6" s="12" t="s">
+        <v>63</v>
+      </c>
+      <c r="B6" s="12" t="s">
+        <v>64</v>
+      </c>
+      <c r="C6" s="12" t="s">
         <v>65</v>
-      </c>
-      <c r="B6" s="12" t="s">
-        <v>66</v>
-      </c>
-      <c r="C6" s="12" t="s">
-        <v>67</v>
       </c>
     </row>
     <row r="7" spans="1:3">
       <c r="A7" s="12" t="s">
-        <v>68</v>
+        <v>66</v>
       </c>
       <c r="B7" s="12" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C7" s="12" t="s">
-        <v>69</v>
+        <v>67</v>
       </c>
     </row>
     <row r="8" spans="1:3" ht="48" customHeight="1">
       <c r="A8" s="12" t="s">
-        <v>70</v>
+        <v>68</v>
       </c>
       <c r="B8" s="12" t="s">
-        <v>59</v>
+        <v>57</v>
       </c>
       <c r="C8" s="12" t="s">
-        <v>71</v>
+        <v>69</v>
       </c>
     </row>
   </sheetData>
@@ -2964,7 +2763,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0400-000000000000}">
   <dimension ref="A1:C23"/>
   <sheetFormatPr defaultColWidth="8.88671875" defaultRowHeight="18"/>
@@ -2977,255 +2776,255 @@
   <sheetData>
     <row r="1" spans="1:3">
       <c r="A1" s="13" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="13" t="s">
         <v>1</v>
       </c>
-      <c r="B1" s="13" t="s">
+      <c r="C1" s="13" t="s">
         <v>2</v>
-      </c>
-      <c r="C1" s="13" t="s">
-        <v>3</v>
       </c>
     </row>
     <row r="2" spans="1:3" ht="36">
       <c r="A2" s="12" t="s">
-        <v>72</v>
+        <v>70</v>
       </c>
       <c r="B2" s="12" t="s">
-        <v>59</v>
+        <v>57</v>
       </c>
       <c r="C2" s="12" t="s">
-        <v>73</v>
+        <v>71</v>
       </c>
     </row>
     <row r="3" spans="1:3">
       <c r="A3" s="12" t="s">
-        <v>61</v>
+        <v>59</v>
       </c>
       <c r="B3" s="12" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C3" s="12" t="s">
-        <v>74</v>
+        <v>72</v>
       </c>
     </row>
     <row r="4" spans="1:3" ht="36">
       <c r="A4" s="12" t="s">
-        <v>75</v>
+        <v>73</v>
       </c>
       <c r="B4" s="12" t="s">
-        <v>66</v>
+        <v>64</v>
       </c>
       <c r="C4" s="12" t="s">
-        <v>76</v>
+        <v>74</v>
       </c>
     </row>
     <row r="5" spans="1:3" ht="36">
       <c r="A5" s="12" t="s">
-        <v>77</v>
+        <v>75</v>
       </c>
       <c r="B5" s="12" t="s">
-        <v>66</v>
+        <v>64</v>
       </c>
       <c r="C5" s="12" t="s">
-        <v>78</v>
+        <v>76</v>
       </c>
     </row>
     <row r="6" spans="1:3">
       <c r="A6" s="12" t="s">
-        <v>79</v>
+        <v>77</v>
       </c>
       <c r="B6" s="12" t="s">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="C6" s="12" t="s">
-        <v>80</v>
+        <v>78</v>
       </c>
     </row>
     <row r="7" spans="1:3" ht="36">
       <c r="A7" s="12" t="s">
-        <v>81</v>
+        <v>79</v>
       </c>
       <c r="B7" s="12" t="s">
-        <v>59</v>
+        <v>57</v>
       </c>
       <c r="C7" s="12" t="s">
-        <v>82</v>
+        <v>80</v>
       </c>
     </row>
     <row r="8" spans="1:3" ht="36">
       <c r="A8" s="12" t="s">
-        <v>83</v>
+        <v>81</v>
       </c>
       <c r="B8" s="12" t="s">
-        <v>59</v>
+        <v>57</v>
       </c>
       <c r="C8" s="12" t="s">
-        <v>84</v>
+        <v>82</v>
       </c>
     </row>
     <row r="9" spans="1:3" ht="36">
       <c r="A9" s="12" t="s">
-        <v>85</v>
+        <v>83</v>
       </c>
       <c r="B9" s="12" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C9" s="12" t="s">
-        <v>86</v>
+        <v>84</v>
       </c>
     </row>
     <row r="10" spans="1:3" ht="36">
       <c r="A10" s="12" t="s">
-        <v>87</v>
+        <v>85</v>
       </c>
       <c r="B10" s="12" t="s">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="C10" s="12" t="s">
-        <v>88</v>
+        <v>86</v>
       </c>
     </row>
     <row r="11" spans="1:3" ht="36">
       <c r="A11" s="12" t="s">
-        <v>89</v>
+        <v>87</v>
       </c>
       <c r="B11" s="12" t="s">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="C11" s="12" t="s">
-        <v>90</v>
+        <v>88</v>
       </c>
     </row>
     <row r="12" spans="1:3" ht="36">
       <c r="A12" s="12" t="s">
-        <v>91</v>
+        <v>89</v>
       </c>
       <c r="B12" s="12" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C12" s="12" t="s">
-        <v>92</v>
+        <v>90</v>
       </c>
     </row>
     <row r="13" spans="1:3" ht="36">
       <c r="A13" s="12" t="s">
-        <v>93</v>
+        <v>91</v>
       </c>
       <c r="B13" s="12" t="s">
-        <v>59</v>
+        <v>57</v>
       </c>
       <c r="C13" s="12" t="s">
-        <v>94</v>
+        <v>92</v>
       </c>
     </row>
     <row r="14" spans="1:3" ht="36">
       <c r="A14" s="12" t="s">
-        <v>95</v>
+        <v>93</v>
       </c>
       <c r="B14" s="12" t="s">
-        <v>66</v>
+        <v>64</v>
       </c>
       <c r="C14" s="12" t="s">
-        <v>96</v>
+        <v>94</v>
       </c>
     </row>
     <row r="15" spans="1:3">
       <c r="A15" s="12" t="s">
-        <v>97</v>
+        <v>95</v>
       </c>
       <c r="B15" s="12" t="s">
-        <v>59</v>
+        <v>57</v>
       </c>
       <c r="C15" s="12" t="s">
-        <v>98</v>
+        <v>96</v>
       </c>
     </row>
     <row r="16" spans="1:3">
       <c r="A16" s="12" t="s">
+        <v>97</v>
+      </c>
+      <c r="B16" s="12" t="s">
+        <v>98</v>
+      </c>
+      <c r="C16" s="12" t="s">
         <v>99</v>
-      </c>
-      <c r="B16" s="12" t="s">
-        <v>100</v>
-      </c>
-      <c r="C16" s="12" t="s">
-        <v>101</v>
       </c>
     </row>
     <row r="17" spans="1:3">
       <c r="A17" s="12" t="s">
-        <v>102</v>
+        <v>100</v>
       </c>
       <c r="B17" s="12" t="s">
-        <v>59</v>
+        <v>57</v>
       </c>
       <c r="C17" s="12" t="s">
-        <v>103</v>
+        <v>101</v>
       </c>
     </row>
     <row r="18" spans="1:3">
       <c r="A18" s="12" t="s">
-        <v>104</v>
+        <v>102</v>
       </c>
       <c r="B18" s="12" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C18" s="12" t="s">
-        <v>105</v>
+        <v>103</v>
       </c>
     </row>
     <row r="19" spans="1:3">
       <c r="A19" s="12" t="s">
-        <v>106</v>
+        <v>104</v>
       </c>
       <c r="B19" s="12" t="s">
-        <v>59</v>
+        <v>57</v>
       </c>
       <c r="C19" s="12" t="s">
-        <v>107</v>
+        <v>105</v>
       </c>
     </row>
     <row r="20" spans="1:3" ht="36">
       <c r="A20" s="12" t="s">
-        <v>108</v>
+        <v>106</v>
       </c>
       <c r="B20" s="12" t="s">
-        <v>59</v>
+        <v>57</v>
       </c>
       <c r="C20" s="12" t="s">
-        <v>109</v>
+        <v>107</v>
       </c>
     </row>
     <row r="21" spans="1:3">
       <c r="A21" s="12" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="B21" s="12" t="s">
-        <v>59</v>
+        <v>57</v>
       </c>
       <c r="C21" s="12" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
     </row>
     <row r="22" spans="1:3">
       <c r="A22" s="12" t="s">
-        <v>111</v>
+        <v>109</v>
       </c>
       <c r="B22" s="12" t="s">
-        <v>59</v>
+        <v>57</v>
       </c>
       <c r="C22" s="12" t="s">
-        <v>112</v>
+        <v>110</v>
       </c>
     </row>
     <row r="23" spans="1:3">
       <c r="A23" s="12" t="s">
-        <v>113</v>
+        <v>111</v>
       </c>
       <c r="B23" s="12" t="s">
-        <v>59</v>
+        <v>57</v>
       </c>
       <c r="C23" s="12" t="s">
-        <v>114</v>
+        <v>112</v>
       </c>
     </row>
   </sheetData>
@@ -3233,7 +3032,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0500-000000000000}">
   <dimension ref="A1:C8"/>
   <sheetFormatPr defaultColWidth="8.88671875" defaultRowHeight="18"/>
@@ -3246,90 +3045,90 @@
   <sheetData>
     <row r="1" spans="1:3" s="10" customFormat="1" ht="17.399999999999999">
       <c r="A1" s="11" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="11" t="s">
         <v>1</v>
       </c>
-      <c r="B1" s="11" t="s">
+      <c r="C1" s="11" t="s">
         <v>2</v>
-      </c>
-      <c r="C1" s="11" t="s">
-        <v>3</v>
       </c>
     </row>
     <row r="2" spans="1:3" ht="90">
       <c r="A2" s="12" t="s">
-        <v>115</v>
+        <v>113</v>
       </c>
       <c r="B2" s="12" t="s">
-        <v>66</v>
+        <v>64</v>
       </c>
       <c r="C2" s="12" t="s">
-        <v>116</v>
+        <v>114</v>
       </c>
     </row>
     <row r="3" spans="1:3" ht="54">
       <c r="A3" s="12" t="s">
+        <v>115</v>
+      </c>
+      <c r="B3" s="12" t="s">
+        <v>116</v>
+      </c>
+      <c r="C3" s="12" t="s">
         <v>117</v>
-      </c>
-      <c r="B3" s="12" t="s">
-        <v>118</v>
-      </c>
-      <c r="C3" s="12" t="s">
-        <v>119</v>
       </c>
     </row>
     <row r="4" spans="1:3" ht="36">
       <c r="A4" s="12" t="s">
-        <v>120</v>
+        <v>118</v>
       </c>
       <c r="B4" s="12" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C4" s="12" t="s">
-        <v>121</v>
+        <v>119</v>
       </c>
     </row>
     <row r="5" spans="1:3" ht="36">
       <c r="A5" s="12" t="s">
-        <v>122</v>
+        <v>120</v>
       </c>
       <c r="B5" s="12" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C5" s="12" t="s">
-        <v>123</v>
+        <v>121</v>
       </c>
     </row>
     <row r="6" spans="1:3" ht="36">
       <c r="A6" s="12" t="s">
-        <v>124</v>
+        <v>122</v>
       </c>
       <c r="B6" s="12" t="s">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="C6" s="12" t="s">
-        <v>125</v>
+        <v>123</v>
       </c>
     </row>
     <row r="7" spans="1:3" ht="36">
       <c r="A7" s="12" t="s">
-        <v>126</v>
+        <v>124</v>
       </c>
       <c r="B7" s="12" t="s">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="C7" s="12" t="s">
-        <v>127</v>
+        <v>125</v>
       </c>
     </row>
     <row r="8" spans="1:3" ht="54">
       <c r="A8" s="12" t="s">
-        <v>128</v>
+        <v>126</v>
       </c>
       <c r="B8" s="12" t="s">
-        <v>59</v>
+        <v>57</v>
       </c>
       <c r="C8" s="12" t="s">
-        <v>129</v>
+        <v>127</v>
       </c>
     </row>
   </sheetData>
@@ -3337,7 +3136,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0700-000000000000}">
   <dimension ref="A1:C18"/>
   <sheetFormatPr defaultColWidth="8.88671875" defaultRowHeight="14.4"/>
@@ -3349,200 +3148,200 @@
   <sheetData>
     <row r="1" spans="1:3" s="9" customFormat="1" ht="17.399999999999999">
       <c r="A1" s="7" t="s">
-        <v>130</v>
+        <v>128</v>
       </c>
       <c r="B1" s="7" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="7" t="s">
         <v>2</v>
-      </c>
-      <c r="C1" s="7" t="s">
-        <v>3</v>
       </c>
     </row>
     <row r="2" spans="1:3" ht="54">
       <c r="A2" s="8" t="s">
+        <v>131</v>
+      </c>
+      <c r="B2" s="8" t="s">
+        <v>132</v>
+      </c>
+      <c r="C2" s="8" t="s">
         <v>133</v>
-      </c>
-      <c r="B2" s="8" t="s">
-        <v>134</v>
-      </c>
-      <c r="C2" s="8" t="s">
-        <v>135</v>
       </c>
     </row>
     <row r="3" spans="1:3" ht="54">
       <c r="A3" s="8" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="B3" s="8" t="s">
-        <v>131</v>
+        <v>129</v>
       </c>
       <c r="C3" s="8" t="s">
-        <v>136</v>
+        <v>134</v>
       </c>
     </row>
     <row r="4" spans="1:3" ht="36">
       <c r="A4" s="8" t="s">
-        <v>137</v>
+        <v>135</v>
       </c>
       <c r="B4" s="8" t="s">
-        <v>131</v>
+        <v>129</v>
       </c>
       <c r="C4" s="8" t="s">
-        <v>138</v>
+        <v>136</v>
       </c>
     </row>
     <row r="5" spans="1:3" ht="36">
       <c r="A5" s="8" t="s">
-        <v>139</v>
+        <v>137</v>
       </c>
       <c r="B5" s="8" t="s">
-        <v>131</v>
+        <v>129</v>
       </c>
       <c r="C5" s="8" t="s">
-        <v>140</v>
+        <v>138</v>
       </c>
     </row>
     <row r="6" spans="1:3" ht="36">
       <c r="A6" s="8" t="s">
-        <v>141</v>
+        <v>139</v>
       </c>
       <c r="B6" s="8" t="s">
-        <v>131</v>
+        <v>129</v>
       </c>
       <c r="C6" s="8" t="s">
-        <v>142</v>
+        <v>140</v>
       </c>
     </row>
     <row r="7" spans="1:3" ht="36">
       <c r="A7" s="8" t="s">
-        <v>143</v>
+        <v>141</v>
       </c>
       <c r="B7" s="8" t="s">
-        <v>131</v>
+        <v>129</v>
       </c>
       <c r="C7" s="8" t="s">
-        <v>144</v>
+        <v>142</v>
       </c>
     </row>
     <row r="8" spans="1:3" ht="54">
       <c r="A8" s="8" t="s">
+        <v>143</v>
+      </c>
+      <c r="B8" s="8" t="s">
+        <v>144</v>
+      </c>
+      <c r="C8" s="8" t="s">
         <v>145</v>
-      </c>
-      <c r="B8" s="8" t="s">
-        <v>146</v>
-      </c>
-      <c r="C8" s="8" t="s">
-        <v>147</v>
       </c>
     </row>
     <row r="9" spans="1:3" ht="54">
       <c r="A9" s="8" t="s">
-        <v>148</v>
+        <v>146</v>
       </c>
       <c r="B9" s="8" t="s">
-        <v>146</v>
+        <v>144</v>
       </c>
       <c r="C9" s="8" t="s">
-        <v>149</v>
+        <v>147</v>
       </c>
     </row>
     <row r="10" spans="1:3" ht="36">
       <c r="A10" s="8" t="s">
+        <v>148</v>
+      </c>
+      <c r="B10" s="8" t="s">
+        <v>149</v>
+      </c>
+      <c r="C10" s="8" t="s">
         <v>150</v>
-      </c>
-      <c r="B10" s="8" t="s">
-        <v>151</v>
-      </c>
-      <c r="C10" s="8" t="s">
-        <v>152</v>
       </c>
     </row>
     <row r="11" spans="1:3" ht="54">
       <c r="A11" s="8" t="s">
-        <v>153</v>
+        <v>151</v>
       </c>
       <c r="B11" s="8" t="s">
-        <v>151</v>
+        <v>149</v>
       </c>
       <c r="C11" s="8" t="s">
-        <v>154</v>
+        <v>152</v>
       </c>
     </row>
     <row r="12" spans="1:3" ht="54">
       <c r="A12" s="8" t="s">
-        <v>155</v>
+        <v>153</v>
       </c>
       <c r="B12" s="8" t="s">
-        <v>151</v>
+        <v>149</v>
       </c>
       <c r="C12" s="8" t="s">
-        <v>156</v>
+        <v>154</v>
       </c>
     </row>
     <row r="13" spans="1:3" ht="54">
       <c r="A13" s="8" t="s">
-        <v>157</v>
+        <v>155</v>
       </c>
       <c r="B13" s="8" t="s">
-        <v>146</v>
+        <v>144</v>
       </c>
       <c r="C13" s="8" t="s">
-        <v>158</v>
+        <v>156</v>
       </c>
     </row>
     <row r="14" spans="1:3" ht="36">
       <c r="A14" s="8" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="B14" s="8" t="s">
-        <v>132</v>
+        <v>130</v>
       </c>
       <c r="C14" s="8" t="s">
-        <v>159</v>
+        <v>157</v>
       </c>
     </row>
     <row r="15" spans="1:3" ht="54">
       <c r="A15" s="8" t="s">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="B15" s="8" t="s">
-        <v>132</v>
+        <v>130</v>
       </c>
       <c r="C15" s="8" t="s">
-        <v>160</v>
+        <v>158</v>
       </c>
     </row>
     <row r="16" spans="1:3" ht="54">
       <c r="A16" s="8" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="B16" s="8" t="s">
-        <v>132</v>
+        <v>130</v>
       </c>
       <c r="C16" s="8" t="s">
-        <v>161</v>
+        <v>159</v>
       </c>
     </row>
     <row r="17" spans="1:3" ht="36">
       <c r="A17" s="8" t="s">
-        <v>162</v>
+        <v>160</v>
       </c>
       <c r="B17" s="8" t="s">
-        <v>131</v>
+        <v>129</v>
       </c>
       <c r="C17" s="8" t="s">
-        <v>163</v>
+        <v>161</v>
       </c>
     </row>
     <row r="18" spans="1:3" ht="36">
       <c r="A18" s="8" t="s">
-        <v>164</v>
+        <v>162</v>
       </c>
       <c r="B18" s="8" t="s">
-        <v>131</v>
+        <v>129</v>
       </c>
       <c r="C18" s="8" t="s">
-        <v>165</v>
+        <v>163</v>
       </c>
     </row>
   </sheetData>
@@ -3550,7 +3349,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{2EE4F384-0682-4B7B-8DBB-A7CBD3E6E09C}">
   <dimension ref="A1:C3"/>
   <sheetFormatPr defaultRowHeight="14.4"/>
@@ -3560,37 +3359,37 @@
     <col min="3" max="3" width="37" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" ht="42" thickBot="1">
-      <c r="A1" s="21" t="s">
-        <v>130</v>
-      </c>
-      <c r="B1" s="21" t="s">
+    <row r="1" spans="1:3" ht="28.2" thickBot="1">
+      <c r="A1" s="19" t="s">
+        <v>128</v>
+      </c>
+      <c r="B1" s="19" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="19" t="s">
         <v>2</v>
       </c>
-      <c r="C1" s="21" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="2" spans="1:3" ht="193.8" thickBot="1">
-      <c r="A2" s="22" t="s">
-        <v>7</v>
-      </c>
-      <c r="B2" s="23" t="s">
-        <v>5</v>
-      </c>
-      <c r="C2" s="23" t="s">
-        <v>262</v>
-      </c>
-    </row>
-    <row r="3" spans="1:3" ht="177.6" thickBot="1">
-      <c r="A3" s="22" t="s">
-        <v>257</v>
-      </c>
-      <c r="B3" s="23" t="s">
-        <v>10</v>
-      </c>
-      <c r="C3" s="23" t="s">
-        <v>263</v>
+    </row>
+    <row r="2" spans="1:3" ht="28.2" thickBot="1">
+      <c r="A2" s="20" t="s">
+        <v>6</v>
+      </c>
+      <c r="B2" s="21" t="s">
+        <v>4</v>
+      </c>
+      <c r="C2" s="21" t="s">
+        <v>260</v>
+      </c>
+    </row>
+    <row r="3" spans="1:3" ht="28.2" thickBot="1">
+      <c r="A3" s="20" t="s">
+        <v>255</v>
+      </c>
+      <c r="B3" s="21" t="s">
+        <v>9</v>
+      </c>
+      <c r="C3" s="21" t="s">
+        <v>261</v>
       </c>
     </row>
   </sheetData>
@@ -3598,7 +3397,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0800-000000000000}">
   <dimension ref="A1:C18"/>
   <sheetFormatPr defaultColWidth="8.88671875" defaultRowHeight="18"/>
@@ -3611,203 +3410,262 @@
   <sheetData>
     <row r="1" spans="1:3" s="6" customFormat="1">
       <c r="A1" s="7" t="s">
-        <v>130</v>
+        <v>128</v>
       </c>
       <c r="B1" s="7" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="7" t="s">
         <v>2</v>
-      </c>
-      <c r="C1" s="7" t="s">
-        <v>3</v>
       </c>
     </row>
     <row r="2" spans="1:3" ht="54">
       <c r="A2" s="8" t="s">
-        <v>61</v>
+        <v>59</v>
       </c>
       <c r="B2" s="8" t="s">
-        <v>131</v>
+        <v>129</v>
       </c>
       <c r="C2" s="8" t="s">
-        <v>166</v>
+        <v>164</v>
       </c>
     </row>
     <row r="3" spans="1:3" ht="36">
       <c r="A3" s="8" t="s">
-        <v>167</v>
+        <v>165</v>
       </c>
       <c r="B3" s="8" t="s">
-        <v>134</v>
+        <v>132</v>
       </c>
       <c r="C3" s="8" t="s">
-        <v>168</v>
+        <v>166</v>
       </c>
     </row>
     <row r="4" spans="1:3" ht="36">
       <c r="A4" s="8" t="s">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="B4" s="8" t="s">
-        <v>131</v>
+        <v>129</v>
       </c>
       <c r="C4" s="8" t="s">
-        <v>169</v>
+        <v>167</v>
       </c>
     </row>
     <row r="5" spans="1:3" ht="54">
       <c r="A5" s="8" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="B5" s="8" t="s">
-        <v>131</v>
+        <v>129</v>
       </c>
       <c r="C5" s="8" t="s">
-        <v>170</v>
+        <v>168</v>
       </c>
     </row>
     <row r="6" spans="1:3" ht="54">
       <c r="A6" s="8" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="B6" s="8" t="s">
-        <v>132</v>
+        <v>130</v>
       </c>
       <c r="C6" s="8" t="s">
-        <v>171</v>
+        <v>169</v>
       </c>
     </row>
     <row r="7" spans="1:3" ht="36">
       <c r="A7" s="8" t="s">
-        <v>111</v>
+        <v>109</v>
       </c>
       <c r="B7" s="8" t="s">
-        <v>132</v>
+        <v>130</v>
       </c>
       <c r="C7" s="8" t="s">
-        <v>172</v>
+        <v>170</v>
       </c>
     </row>
     <row r="8" spans="1:3" ht="36">
       <c r="A8" s="8" t="s">
-        <v>113</v>
+        <v>111</v>
       </c>
       <c r="B8" s="8" t="s">
-        <v>132</v>
+        <v>130</v>
       </c>
       <c r="C8" s="8" t="s">
-        <v>173</v>
+        <v>171</v>
       </c>
     </row>
     <row r="9" spans="1:3" ht="54">
       <c r="A9" s="8" t="s">
-        <v>174</v>
+        <v>172</v>
       </c>
       <c r="B9" s="8" t="s">
-        <v>132</v>
+        <v>130</v>
       </c>
       <c r="C9" s="8" t="s">
-        <v>175</v>
+        <v>173</v>
       </c>
     </row>
     <row r="10" spans="1:3" ht="72">
       <c r="A10" s="8" t="s">
-        <v>176</v>
+        <v>174</v>
       </c>
       <c r="B10" s="8" t="s">
-        <v>132</v>
+        <v>130</v>
       </c>
       <c r="C10" s="8" t="s">
-        <v>177</v>
+        <v>175</v>
       </c>
     </row>
     <row r="11" spans="1:3" ht="36">
       <c r="A11" s="8" t="s">
-        <v>178</v>
+        <v>176</v>
       </c>
       <c r="B11" s="8" t="s">
-        <v>132</v>
+        <v>130</v>
       </c>
       <c r="C11" s="8" t="s">
-        <v>179</v>
+        <v>177</v>
       </c>
     </row>
     <row r="12" spans="1:3" ht="90">
       <c r="A12" s="8" t="s">
+        <v>178</v>
+      </c>
+      <c r="B12" s="8" t="s">
+        <v>130</v>
+      </c>
+      <c r="C12" s="8" t="s">
+        <v>179</v>
+      </c>
+    </row>
+    <row r="13" spans="1:3" ht="54">
+      <c r="A13" s="17" t="s">
         <v>180</v>
       </c>
-      <c r="B12" s="8" t="s">
-        <v>132</v>
-      </c>
-      <c r="C12" s="8" t="s">
+      <c r="B13" s="8" t="s">
+        <v>130</v>
+      </c>
+      <c r="C13" s="17" t="s">
         <v>181</v>
       </c>
     </row>
-    <row r="13" spans="1:3" ht="54">
-      <c r="A13" s="19" t="s">
+    <row r="14" spans="1:3" ht="36">
+      <c r="A14" s="17" t="s">
         <v>182</v>
       </c>
-      <c r="B13" s="8" t="s">
-        <v>132</v>
-      </c>
-      <c r="C13" s="19" t="s">
+      <c r="B14" s="8" t="s">
+        <v>130</v>
+      </c>
+      <c r="C14" s="17" t="s">
         <v>183</v>
-      </c>
-    </row>
-    <row r="14" spans="1:3" ht="36">
-      <c r="A14" s="19" t="s">
-        <v>184</v>
-      </c>
-      <c r="B14" s="8" t="s">
-        <v>132</v>
-      </c>
-      <c r="C14" s="19" t="s">
-        <v>185</v>
       </c>
     </row>
     <row r="15" spans="1:3" ht="36">
       <c r="A15" s="8" t="s">
-        <v>186</v>
+        <v>184</v>
       </c>
       <c r="B15" s="8" t="s">
-        <v>132</v>
+        <v>130</v>
       </c>
       <c r="C15" s="8" t="s">
-        <v>187</v>
+        <v>185</v>
       </c>
     </row>
     <row r="16" spans="1:3" ht="54">
       <c r="A16" s="8" t="s">
+        <v>186</v>
+      </c>
+      <c r="B16" s="8" t="s">
+        <v>130</v>
+      </c>
+      <c r="C16" s="8" t="s">
+        <v>187</v>
+      </c>
+    </row>
+    <row r="17" spans="1:3" ht="54">
+      <c r="A17" s="17" t="s">
         <v>188</v>
       </c>
-      <c r="B16" s="8" t="s">
-        <v>132</v>
-      </c>
-      <c r="C16" s="8" t="s">
+      <c r="B17" s="8" t="s">
+        <v>129</v>
+      </c>
+      <c r="C17" s="17" t="s">
         <v>189</v>
-      </c>
-    </row>
-    <row r="17" spans="1:3" ht="54">
-      <c r="A17" s="19" t="s">
-        <v>190</v>
-      </c>
-      <c r="B17" s="8" t="s">
-        <v>131</v>
-      </c>
-      <c r="C17" s="19" t="s">
-        <v>191</v>
       </c>
     </row>
     <row r="18" spans="1:3" ht="72">
       <c r="A18" s="8" t="s">
+        <v>190</v>
+      </c>
+      <c r="B18" s="8" t="s">
+        <v>191</v>
+      </c>
+      <c r="C18" s="8" t="s">
         <v>192</v>
-      </c>
-      <c r="B18" s="8" t="s">
-        <v>193</v>
-      </c>
-      <c r="C18" s="8" t="s">
-        <v>194</v>
       </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{61EFBDAE-EAB8-41C5-BB88-AE4529FFB780}">
+  <dimension ref="A1:C4"/>
+  <sheetFormatPr defaultRowHeight="14.4"/>
+  <cols>
+    <col min="1" max="1" width="16.5546875" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="11" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="64.44140625" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:3">
+      <c r="A1" s="16" t="s">
+        <v>128</v>
+      </c>
+      <c r="B1" s="16" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="16" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="2" spans="1:3">
+      <c r="A2" t="s">
+        <v>180</v>
+      </c>
+      <c r="B2" s="18" t="s">
+        <v>130</v>
+      </c>
+      <c r="C2" t="s">
+        <v>181</v>
+      </c>
+    </row>
+    <row r="3" spans="1:3">
+      <c r="A3" t="s">
+        <v>182</v>
+      </c>
+      <c r="B3" s="18" t="s">
+        <v>130</v>
+      </c>
+      <c r="C3" t="s">
+        <v>183</v>
+      </c>
+    </row>
+    <row r="4" spans="1:3">
+      <c r="A4" t="s">
+        <v>188</v>
+      </c>
+      <c r="B4" s="18" t="s">
+        <v>129</v>
+      </c>
+      <c r="C4" t="s">
+        <v>189</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
 </file>